--- a/02_outputs/excel/境内策略ETF产品梳理_初版.xlsx
+++ b/02_outputs/excel/境内策略ETF产品梳理_初版.xlsx
@@ -12,7 +12,7 @@
     <sheet name="指数规则表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'产品总表'!$A$1:$U$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'产品总表'!$A$1:$U$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'策略分类表'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'指数规则表'!$A$1:$P$1</definedName>
   </definedNames>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,10 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -68,10 +72,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -438,30 +445,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:U60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="42" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -571,8 +578,3511 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>红利</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>上证红利</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>华泰柏瑞上证红利ETF</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>510880</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>上证红利指数</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：显示其采用完全复制策略跟踪上证红利指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>红利</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>中证红利</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>招商中证红利ETF</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>515080</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>招商基金</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>中证红利指数</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：显示其为被动式指数基金，跟踪中证红利指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>红利</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>中证红利</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>易方达中证红利ETF</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>515180</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>易方达</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>中证红利指数</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>易方达基金官网：显示代码515180、上交所上市、标的指数为中证红利指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>红利</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>中证红利</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>博时中证红利ETF</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>515890</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>博时基金</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>中证红利指数</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2" t="n"/>
+      <c r="R5" s="2" t="n"/>
+      <c r="S5" s="2" t="n"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：规模/上市日期后续用Wind校验</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>公开ETF列表/基金销售平台：显示其跟踪中证红利指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>红利</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>中证红利</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>汇添富中证红利ETF</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>560020</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>汇添富</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n"/>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>中证红利指数</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
+      <c r="P6" s="2" t="n"/>
+      <c r="Q6" s="2" t="n"/>
+      <c r="R6" s="2" t="n"/>
+      <c r="S6" s="2" t="n"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：规模/上市日期后续用Wind校验</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>公开ETF列表/基金销售平台：显示其跟踪中证红利指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>红利</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>中证红利</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>广发中证红利ETF</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>159589</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>广发基金</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n"/>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>中证红利指数</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
+      <c r="P7" s="2" t="n"/>
+      <c r="Q7" s="2" t="n"/>
+      <c r="R7" s="2" t="n"/>
+      <c r="S7" s="2" t="n"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：规模/上市日期后续用Wind校验</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>公开ETF列表/基金销售平台：显示其跟踪中证红利指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>红利</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>中证红利</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>万家中证红利ETF</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>159581</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>万家基金</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n"/>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>中证红利指数</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" s="2" t="n"/>
+      <c r="M8" s="2" t="n"/>
+      <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
+      <c r="P8" s="2" t="n"/>
+      <c r="Q8" s="2" t="n"/>
+      <c r="R8" s="2" t="n"/>
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：规模/上市日期后续用Wind校验</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>公开ETF列表/基金销售平台：显示其跟踪中证红利指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>红利</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>深证红利</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>工银深证红利ETF</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>159905</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>工银瑞信</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n"/>
+      <c r="H9" s="2" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>深证红利股票指数</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n"/>
+      <c r="K9" s="2" t="n"/>
+      <c r="L9" s="2" t="n"/>
+      <c r="M9" s="2" t="n"/>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
+      <c r="P9" s="2" t="n"/>
+      <c r="Q9" s="2" t="n"/>
+      <c r="R9" s="2" t="n"/>
+      <c r="S9" s="2" t="n"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：显示其跟踪深证红利股票指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>红利</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>深证红利</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>西部利得深证红利ETF</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>159708</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>西部利得</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n"/>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>深证红利指数</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
+      <c r="L10" s="2" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="n"/>
+      <c r="P10" s="2" t="n"/>
+      <c r="Q10" s="2" t="n"/>
+      <c r="R10" s="2" t="n"/>
+      <c r="S10" s="2" t="n"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：规模/上市日期后续用Wind校验</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>西部利得基金官网：显示业绩基准为深证红利指数收益率</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>高股息</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>智选高股息</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>广发中证智选高股息策略ETF</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>159207</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>广发基金</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n"/>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>中证智选高股息策略指数</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="n"/>
+      <c r="P11" s="2" t="n"/>
+      <c r="Q11" s="2" t="n"/>
+      <c r="R11" s="2" t="n"/>
+      <c r="S11" s="2" t="n"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：新产品需校验规模与上市日期</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>广发基金官网：显示代码159207，业绩基准为中证智选高股息策略指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>红利低波</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>中证红利低波动</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>华泰柏瑞中证红利低波动ETF</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>512890</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>中证红利低波动指数</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="n"/>
+      <c r="R12" s="2" t="n"/>
+      <c r="S12" s="2" t="n"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线重点</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：显示其跟踪中证红利低波动指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>红利低波</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>中证红利低波动100</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>景顺长城中证红利低波动100ETF</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>515100</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>景顺长城</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n"/>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2" t="n"/>
+      <c r="R13" s="2" t="n"/>
+      <c r="S13" s="2" t="n"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线重点</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>景顺长城基金官网：显示代码515100，业绩基准为中证红利低波动100指数收益率</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>红利低波</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪深300红利低波</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>嘉实沪深300红利低波动ETF</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>515300</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>嘉实基金</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>沪深300红利低波动指数</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="n"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：规模/上市日期后续用Wind校验</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>公开基金资料：显示该产品跟踪300红利低波指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>红利低波</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>标普A股红利低波</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>南方标普中国A股大盘红利低波50ETF</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>515450</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>南方基金</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n"/>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>标普中国A股大盘红利低波50指数</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="2" t="n"/>
+      <c r="O15" s="2" t="n"/>
+      <c r="P15" s="2" t="n"/>
+      <c r="Q15" s="2" t="n"/>
+      <c r="R15" s="2" t="n"/>
+      <c r="S15" s="2" t="n"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线重点</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/标普官网：显示其跟踪标普中国A股大盘红利低波50指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>红利低波</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>A500红利低波</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>平安中证A500红利低波动ETF</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>561680</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>平安基金</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n"/>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>中证A500红利低波动指数</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="n"/>
+      <c r="P16" s="2" t="n"/>
+      <c r="Q16" s="2" t="n"/>
+      <c r="R16" s="2" t="n"/>
+      <c r="S16" s="2" t="n"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：新产品需校验规模/上市日期</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>平安基金资料：显示标的指数为中证A500红利低波动指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>红利低波</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>A500红利低波</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>易方达中证A500红利低波动ETF</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>563510</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>易方达</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>中证A500红利低波动指数</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
+      <c r="L17" s="2" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="n"/>
+      <c r="P17" s="2" t="n"/>
+      <c r="Q17" s="2" t="n"/>
+      <c r="R17" s="2" t="n"/>
+      <c r="S17" s="2" t="n"/>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：新产品需校验规模/上市日期</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>易方达基金官网：显示该指数从中证A500中选取连续分红、股息率高且波动率低的50只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>红利低波</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>A500红利低波</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>A500红利低波ETF</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>159296</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>待校验</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n"/>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>中证A500红利低波动指数</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n"/>
+      <c r="K18" s="2" t="n"/>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="n"/>
+      <c r="O18" s="2" t="n"/>
+      <c r="P18" s="2" t="n"/>
+      <c r="Q18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
+      <c r="S18" s="2" t="n"/>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：管理人和产品全称待Wind校验</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>公开资料：显示首批跟踪中证A500红利低波动指数的产品包含深市产品</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>红利低波</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>红利低波100</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>博时中证红利低波100ETF</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>159307</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>博时基金</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n"/>
+      <c r="K19" s="2" t="n"/>
+      <c r="L19" s="2" t="n"/>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="n"/>
+      <c r="P19" s="2" t="n"/>
+      <c r="Q19" s="2" t="n"/>
+      <c r="R19" s="2" t="n"/>
+      <c r="S19" s="2" t="n"/>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：基金全称/规模/上市日期需Wind校验</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>公开基金销售平台：可检索到红利低波100ETF线索</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>低波</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪深300低波</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>华安沪深300行业中性低波ETF</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>512270</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>华安基金</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n"/>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>沪深300行业中性低波动指数</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="n"/>
+      <c r="R20" s="2" t="n"/>
+      <c r="S20" s="2" t="n"/>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>华安基金产品资料概要：显示代码512270，标的指数为沪深300行业中性低波动指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>低波</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>中证500低波</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>华安中证500行业中性低波ETF</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>512260</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>华安基金</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n"/>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>中证500行业中性低波动指数</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n"/>
+      <c r="K21" s="2" t="n"/>
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="n"/>
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="n"/>
+      <c r="P21" s="2" t="n"/>
+      <c r="Q21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="n"/>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>华安基金官网：显示产品代码512260，跟踪中证500行业中性低波动指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>国证自由现金流</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>华夏国证自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>159201</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>华夏基金</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>国证自由现金流指数</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="n"/>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="n"/>
+      <c r="P22" s="2" t="n"/>
+      <c r="Q22" s="2" t="n"/>
+      <c r="R22" s="2" t="n"/>
+      <c r="S22" s="2" t="n"/>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线重点
+待校验事项：新产品需校验规模/上市日期</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：显示代码159201，基金全称为华夏国证自由现金流ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>国证自由现金流</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>易方达国证自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>159222</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>易方达</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>国证自由现金流指数</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n"/>
+      <c r="P23" s="2" t="n"/>
+      <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="n"/>
+      <c r="S23" s="2" t="n"/>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线重点
+待校验事项：新产品需校验规模/上市日期</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>易方达基金官网：显示代码159222、深交所上市、标的指数为国证自由现金流指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>富时规模/上市日期</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>易方达基金官网：显示代码159222、深交所上市、标的指数为国证自由现金流指数</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n"/>
+      <c r="P24" s="2" t="n"/>
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="n"/>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>富时自由现金流聚焦</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>国泰富时中国A股自由现金流聚焦ETF</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>159399</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>国泰基金</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n"/>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>富时中国A股自由现金流聚焦指数</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n"/>
+      <c r="K25" s="2" t="n"/>
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
+      <c r="P25" s="2" t="n"/>
+      <c r="Q25" s="2" t="n"/>
+      <c r="R25" s="2" t="n"/>
+      <c r="S25" s="2" t="n"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：指数细节和上市日期需Wind校验</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>公开资料：显示其属于自由现金流聚焦方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>广发自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>159229</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>广发基金</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n"/>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流相关指数</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="n"/>
+      <c r="O26" s="2" t="n"/>
+      <c r="P26" s="2" t="n"/>
+      <c r="Q26" s="2" t="n"/>
+      <c r="R26" s="2" t="n"/>
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：跟踪指数全称需Wind校验</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：可检索到自由现金流ETF广发159229</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>工银自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>159236</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>工银瑞信</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流相关指数</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n"/>
+      <c r="K27" s="2" t="n"/>
+      <c r="L27" s="2" t="n"/>
+      <c r="M27" s="2" t="n"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="2" t="n"/>
+      <c r="P27" s="2" t="n"/>
+      <c r="Q27" s="2" t="n"/>
+      <c r="R27" s="2" t="n"/>
+      <c r="S27" s="2" t="n"/>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：跟踪指数全称需Wind校验</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：可检索到自由现金流ETF工银159236</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>中证全指自由现金流</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>平安中证全指自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>159233</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>平安基金</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n"/>
+      <c r="H28" s="2" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>中证全指自由现金流指数</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n"/>
+      <c r="K28" s="2" t="n"/>
+      <c r="L28" s="2" t="n"/>
+      <c r="M28" s="2" t="n"/>
+      <c r="N28" s="2" t="n"/>
+      <c r="O28" s="2" t="n"/>
+      <c r="P28" s="2" t="n"/>
+      <c r="Q28" s="2" t="n"/>
+      <c r="R28" s="2" t="n"/>
+      <c r="S28" s="2" t="n"/>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：新产品需校验规模/上市日期</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>平安基金官网：显示代码159233，标的指数为中证全指自由现金流指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>中证全指自由现金流</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>兴业中证全指自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>563620</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>兴业基金</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>中证全指自由现金流指数</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n"/>
+      <c r="K29" s="2" t="n"/>
+      <c r="L29" s="2" t="n"/>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
+      <c r="Q29" s="2" t="n"/>
+      <c r="R29" s="2" t="n"/>
+      <c r="S29" s="2" t="n"/>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：新产品需校验规模/上市日期</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>兴业基金官网：显示产品代码563620，法定名称为兴业中证全指自由现金流ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>国证自由现金流</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>银华国证自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>待校验</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>银华基金</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待校验</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n"/>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>国证自由现金流指数</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
+      <c r="L30" s="2" t="n"/>
+      <c r="M30" s="2" t="n"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="n"/>
+      <c r="R30" s="2" t="n"/>
+      <c r="S30" s="2" t="n"/>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：仅作线索
+待校验事项：公开搜索主要找到联接基金，目标ETF代码需Wind校验</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：可检索到银华国证自由现金流联接基金线索</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>国证自由现金流</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>永赢国证自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>待校验</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>永赢基金</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待校验</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n"/>
+      <c r="H31" s="2" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>国证自由现金流指数</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" s="2" t="n"/>
+      <c r="M31" s="2" t="n"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
+      <c r="P31" s="2" t="n"/>
+      <c r="Q31" s="2" t="n"/>
+      <c r="R31" s="2" t="n"/>
+      <c r="S31" s="2" t="n"/>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：仅作线索
+待校验事项：公开搜索主要找到联接基金，目标ETF代码需Wind校验</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：可检索到永赢国证自由现金流联接基金线索</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>国证自由现金流</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>长城国证自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>待校验</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>长城基金</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待校验</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>国证自由现金流指数</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n"/>
+      <c r="K32" s="2" t="n"/>
+      <c r="L32" s="2" t="n"/>
+      <c r="M32" s="2" t="n"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n"/>
+      <c r="P32" s="2" t="n"/>
+      <c r="Q32" s="2" t="n"/>
+      <c r="R32" s="2" t="n"/>
+      <c r="S32" s="2" t="n"/>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：仅作线索
+待校验事项：公开搜索主要找到联接基金，目标ETF代码需Wind校验</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>长城基金官网/公开基金页面：可检索到国证自由现金流联接基金线索</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>质量</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>红利质量</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>华夏中证红利质量ETF</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>159758</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>华夏基金</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n"/>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>中证红利质量指数</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n"/>
+      <c r="K33" s="2" t="n"/>
+      <c r="L33" s="2" t="n"/>
+      <c r="M33" s="2" t="n"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="2" t="n"/>
+      <c r="P33" s="2" t="n"/>
+      <c r="Q33" s="2" t="n"/>
+      <c r="R33" s="2" t="n"/>
+      <c r="S33" s="2" t="n"/>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>华夏基金官网：显示代码159758、基金全称为华夏中证红利质量ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>质量</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>红利质量</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>招商中证全指红利质量ETF</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>159209</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>招商基金</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>中证全指红利质量指数</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="2" t="n"/>
+      <c r="P34" s="2" t="n"/>
+      <c r="Q34" s="2" t="n"/>
+      <c r="R34" s="2" t="n"/>
+      <c r="S34" s="2" t="n"/>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：新产品需校验规模/上市日期</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/招商公告：可检索到红利质量ETF招商159209</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>质量</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>红利质量</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>易方达中证全指红利质量ETF</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>560370</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>易方达</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>中证全指红利质量指数</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="n"/>
+      <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="n"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：新产品需校验规模/上市日期</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>易方达基金官网：可检索到产品代码560370</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>价值</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>价值因子</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>富国中证价值ETF</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>512040</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>富国基金</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n"/>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>中证价值相关指数</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n"/>
+      <c r="K36" s="2" t="n"/>
+      <c r="L36" s="2" t="n"/>
+      <c r="M36" s="2" t="n"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="2" t="n"/>
+      <c r="P36" s="2" t="n"/>
+      <c r="Q36" s="2" t="n"/>
+      <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="n"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：跟踪指数全称需校验</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>富国基金官网：显示基金名称为富国中证价值ETF，代码512040</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>价值</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>国证价值100</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>易方达国证价值100ETF</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>159263</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>易方达</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>国证价值100指数</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="2" t="n"/>
+      <c r="P37" s="2" t="n"/>
+      <c r="Q37" s="2" t="n"/>
+      <c r="R37" s="2" t="n"/>
+      <c r="S37" s="2" t="n"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：新产品需校验规模/上市日期</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>易方达基金官网：显示代码159263，基金名称为易方达国证价值100ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>成长</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>创业板动量成长</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>华夏创业板动量成长ETF</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>159967</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>华夏基金</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n"/>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>创业板动量成长指数/创成长指数</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n"/>
+      <c r="K38" s="2" t="n"/>
+      <c r="L38" s="2" t="n"/>
+      <c r="M38" s="2" t="n"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="2" t="n"/>
+      <c r="P38" s="2" t="n"/>
+      <c r="Q38" s="2" t="n"/>
+      <c r="R38" s="2" t="n"/>
+      <c r="S38" s="2" t="n"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：指数简称和全称需Wind校验</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：可检索到创业板成长ETF华夏159967</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>成长</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>深证成长40</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>大成深证成长40ETF</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>159906</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>大成基金</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>深证成长40指数</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n"/>
+      <c r="K39" s="2" t="n"/>
+      <c r="L39" s="2" t="n"/>
+      <c r="M39" s="2" t="n"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="n"/>
+      <c r="Q39" s="2" t="n"/>
+      <c r="R39" s="2" t="n"/>
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：显示基金全称为深证成长40交易型开放式指数基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>成长</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>科创成长</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>易方达上证科创板成长ETF</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>588020</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>易方达</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n"/>
+      <c r="H40" s="2" t="n"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>上证科创板成长指数</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n"/>
+      <c r="K40" s="2" t="n"/>
+      <c r="L40" s="2" t="n"/>
+      <c r="M40" s="2" t="n"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="2" t="n"/>
+      <c r="P40" s="2" t="n"/>
+      <c r="Q40" s="2" t="n"/>
+      <c r="R40" s="2" t="n"/>
+      <c r="S40" s="2" t="n"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>易方达基金官网：说明该指数从科创板中选取营收与净利润等业绩指标增长率较高的50只证券</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>成长</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>科创成长</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>万家上证科创板成长ETF</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>588070</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>万家基金</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n"/>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>上证科创板成长指数</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="2" t="n"/>
+      <c r="P41" s="2" t="n"/>
+      <c r="Q41" s="2" t="n"/>
+      <c r="R41" s="2" t="n"/>
+      <c r="S41" s="2" t="n"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>万家基金官网：显示标的指数为上证科创板成长指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>成长</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>科创成长</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>南方上证科创板成长ETF</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>589700</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>南方基金</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>上证科创板成长指数</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n"/>
+      <c r="K42" s="2" t="n"/>
+      <c r="L42" s="2" t="n"/>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
+      <c r="O42" s="2" t="n"/>
+      <c r="P42" s="2" t="n"/>
+      <c r="Q42" s="2" t="n"/>
+      <c r="R42" s="2" t="n"/>
+      <c r="S42" s="2" t="n"/>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线
+待校验事项：规模/上市日期后续用Wind校验</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>南方基金官网/上交所公告：可检索到代码589700</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>成长</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>科创成长</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>广发上证科创板成长ETF</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>588110</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>广发基金</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n"/>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>上证科创板成长指数</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n"/>
+      <c r="K43" s="2" t="n"/>
+      <c r="L43" s="2" t="n"/>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="2" t="n"/>
+      <c r="P43" s="2" t="n"/>
+      <c r="Q43" s="2" t="n"/>
+      <c r="R43" s="2" t="n"/>
+      <c r="S43" s="2" t="n"/>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>广发基金官网：显示代码588110，基金名称为广发上证科创板成长ETF</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>基本面策略</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>基本面50</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>嘉实基本面50ETF</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>512750</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>嘉实基金</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>基本面50指数</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n"/>
+      <c r="K44" s="2" t="n"/>
+      <c r="L44" s="2" t="n"/>
+      <c r="M44" s="2" t="n"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="2" t="n"/>
+      <c r="P44" s="2" t="n"/>
+      <c r="Q44" s="2" t="n"/>
+      <c r="R44" s="2" t="n"/>
+      <c r="S44" s="2" t="n"/>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：显示基本面50ETF嘉实为被动式指数化投资产品</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>基本面策略</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>深证基本面120</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>嘉实深证基本面120ETF</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>159910</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>嘉实基金</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n"/>
+      <c r="H45" s="2" t="n"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>深证基本面120指数</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n"/>
+      <c r="K45" s="2" t="n"/>
+      <c r="L45" s="2" t="n"/>
+      <c r="M45" s="2" t="n"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="2" t="n"/>
+      <c r="P45" s="2" t="n"/>
+      <c r="Q45" s="2" t="n"/>
+      <c r="R45" s="2" t="n"/>
+      <c r="S45" s="2" t="n"/>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：主线</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：显示其以跟踪深证基本面120指数为原则</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>多因子/增强</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>指数增强</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>银华中证800增强ETF</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>159517</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>银华基金</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>中证800+指数增强</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="2" t="n"/>
+      <c r="M46" s="2" t="n"/>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="2" t="n"/>
+      <c r="P46" s="2" t="n"/>
+      <c r="Q46" s="2" t="n"/>
+      <c r="R46" s="2" t="n"/>
+      <c r="S46" s="2" t="n"/>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：单列观察
+待校验事项：是否纳入策略ETF主线需问mentor</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：显示该产品采用指数增强投资策略，并使用多因子量化选股</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>多因子/增强</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>指数增强</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>华夏中证A500增强策略ETF</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>512370</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>华夏基金</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n"/>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>中证A500+增强策略</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n"/>
+      <c r="K47" s="2" t="n"/>
+      <c r="L47" s="2" t="n"/>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
+      <c r="P47" s="2" t="n"/>
+      <c r="Q47" s="2" t="n"/>
+      <c r="R47" s="2" t="n"/>
+      <c r="S47" s="2" t="n"/>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：单列观察
+待校验事项：是否纳入策略ETF主线需问mentor</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>华夏基金官网：可检索到代码512370</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>央企股东回报</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>央企股东回报</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>招商中证国新央企股东回报ETF</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>561960</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>招商基金</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>中证国新央企股东回报指数</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n"/>
+      <c r="K48" s="2" t="n"/>
+      <c r="L48" s="2" t="n"/>
+      <c r="M48" s="2" t="n"/>
+      <c r="N48" s="2" t="n"/>
+      <c r="O48" s="2" t="n"/>
+      <c r="P48" s="2" t="n"/>
+      <c r="Q48" s="2" t="n"/>
+      <c r="R48" s="2" t="n"/>
+      <c r="S48" s="2" t="n"/>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：补充观察
+待校验事项：兼具央企主题和股东回报策略属性</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：显示代码561960，跟踪中证国新央企股东回报指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>央企股东回报</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>央企股东回报</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>广发中证国新央企股东回报ETF</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>560700</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>广发基金</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n"/>
+      <c r="H49" s="2" t="n"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>中证国新央企股东回报指数</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n"/>
+      <c r="K49" s="2" t="n"/>
+      <c r="L49" s="2" t="n"/>
+      <c r="M49" s="2" t="n"/>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="2" t="n"/>
+      <c r="P49" s="2" t="n"/>
+      <c r="Q49" s="2" t="n"/>
+      <c r="R49" s="2" t="n"/>
+      <c r="S49" s="2" t="n"/>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：补充观察
+待校验事项：兼具央企主题和股东回报策略属性</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>同花顺基金页面：显示代码560700、管理人为广发基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>央企股东回报</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>央企股东回报</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>汇添富中证国新央企股东回报ETF</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>560070</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>汇添富</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>中证国新央企股东回报指数</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n"/>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="n"/>
+      <c r="N50" s="2" t="n"/>
+      <c r="O50" s="2" t="n"/>
+      <c r="P50" s="2" t="n"/>
+      <c r="Q50" s="2" t="n"/>
+      <c r="R50" s="2" t="n"/>
+      <c r="S50" s="2" t="n"/>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：补充观察
+待校验事项：兼具央企主题和股东回报策略属性</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>汇添富基金官网：可检索到该产品，代码560070</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>央企红利</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>央企红利</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>华泰柏瑞中证中央企业红利ETF</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>561580</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>华泰柏瑞</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n"/>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>中证央企红利指数</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n"/>
+      <c r="K51" s="2" t="n"/>
+      <c r="L51" s="2" t="n"/>
+      <c r="M51" s="2" t="n"/>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="2" t="n"/>
+      <c r="P51" s="2" t="n"/>
+      <c r="Q51" s="2" t="n"/>
+      <c r="R51" s="2" t="n"/>
+      <c r="S51" s="2" t="n"/>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：补充观察
+待校验事项：红利策略与央企主题交叉，是否纳入主线需问mentor</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>公开资料：显示该产品跟踪央企红利指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>国企红利</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>国企红利</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>创金合信国企红利ETF</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>563890</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>创金合信</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n"/>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>国企红利相关指数</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n"/>
+      <c r="K52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="2" t="n"/>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="2" t="n"/>
+      <c r="P52" s="2" t="n"/>
+      <c r="Q52" s="2" t="n"/>
+      <c r="R52" s="2" t="n"/>
+      <c r="S52" s="2" t="n"/>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：补充观察
+待校验事项：指数名称/规模/上市日期需Wind校验</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：可检索到该产品</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>国企红利</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>国企红利</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>国企红利ETF</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>159515</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>待校验</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>中证国有企业红利指数</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n"/>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="n"/>
+      <c r="N53" s="2" t="n"/>
+      <c r="O53" s="2" t="n"/>
+      <c r="P53" s="2" t="n"/>
+      <c r="Q53" s="2" t="n"/>
+      <c r="R53" s="2" t="n"/>
+      <c r="S53" s="2" t="n"/>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：补充观察
+待校验事项：管理人和产品全称待Wind校验</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>公开资料：显示159515跟踪中证国有企业红利指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>国企红利</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>国企红利</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>国泰上证国有企业红利ETF</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>510720</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>国泰基金</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n"/>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>上证国有企业红利相关指数</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n"/>
+      <c r="K54" s="2" t="n"/>
+      <c r="L54" s="2" t="n"/>
+      <c r="M54" s="2" t="n"/>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="2" t="n"/>
+      <c r="P54" s="2" t="n"/>
+      <c r="Q54" s="2" t="n"/>
+      <c r="R54" s="2" t="n"/>
+      <c r="S54" s="2" t="n"/>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：补充观察
+待校验事项：指数名称/规模/上市日期需Wind校验</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>公开基金行情网站：可检索到基金名称、代码和管理人为国泰基金</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>180ESG</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>工银180ESGETF</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>510990</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>工银瑞信</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n"/>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>ESG相关指数</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n"/>
+      <c r="K55" s="2" t="n"/>
+      <c r="L55" s="2" t="n"/>
+      <c r="M55" s="2" t="n"/>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="2" t="n"/>
+      <c r="P55" s="2" t="n"/>
+      <c r="Q55" s="2" t="n"/>
+      <c r="R55" s="2" t="n"/>
+      <c r="S55" s="2" t="n"/>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：补充观察
+待校验事项：ESG是否作为主线需问mentor</t>
+        </is>
+      </c>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：显示该产品采取完全复制策略，跟踪标的指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>央企ESG</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>融通中证诚通央企ESGETF</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>560810</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>融通基金</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n"/>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>中证诚通央企ESG指数</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
+      <c r="M56" s="2" t="n"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="2" t="n"/>
+      <c r="P56" s="2" t="n"/>
+      <c r="Q56" s="2" t="n"/>
+      <c r="R56" s="2" t="n"/>
+      <c r="S56" s="2" t="n"/>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：补充观察
+待校验事项：ESG是否作为主线需问mentor</t>
+        </is>
+      </c>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>融通基金官网：显示产品为融通中证诚通央企ESGETF，代码560810</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>ESG/可持续</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>可持续发展</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>博时中证可持续发展100ETF</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>515090</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>博时基金</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n"/>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>中证可持续发展100指数</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n"/>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="n"/>
+      <c r="N57" s="2" t="n"/>
+      <c r="O57" s="2" t="n"/>
+      <c r="P57" s="2" t="n"/>
+      <c r="Q57" s="2" t="n"/>
+      <c r="R57" s="2" t="n"/>
+      <c r="S57" s="2" t="n"/>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：补充观察
+待校验事项：ESG/可持续是否作为主线需问mentor</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>天天基金/基金F10：显示该产品跟踪中证可持续发展100指数</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>港股通红利</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>港股通央企红利</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>景顺长城中证国新港股通央企红利ETF</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>520990</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>景顺长城</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n"/>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>港股通央企红利相关指数</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n"/>
+      <c r="K58" s="2" t="n"/>
+      <c r="L58" s="2" t="n"/>
+      <c r="M58" s="2" t="n"/>
+      <c r="N58" s="2" t="n"/>
+      <c r="O58" s="2" t="n"/>
+      <c r="P58" s="2" t="n"/>
+      <c r="Q58" s="2" t="n"/>
+      <c r="R58" s="2" t="n"/>
+      <c r="S58" s="2" t="n"/>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：跨境补充
+待校验事项：属于港股通/跨境方向，暂不混入A股主线</t>
+        </is>
+      </c>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>景顺长城基金官网：可检索到产品代码520990</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>港股通红利</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>港股通央企红利</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>华夏中证港股通央企红利ETF</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>513910</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>华夏基金</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>上交所</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n"/>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>港股通央企红利相关指数</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="n"/>
+      <c r="L59" s="2" t="n"/>
+      <c r="M59" s="2" t="n"/>
+      <c r="N59" s="2" t="n"/>
+      <c r="O59" s="2" t="n"/>
+      <c r="P59" s="2" t="n"/>
+      <c r="Q59" s="2" t="n"/>
+      <c r="R59" s="2" t="n"/>
+      <c r="S59" s="2" t="n"/>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：跨境补充
+待校验事项：属于港股通/跨境方向，暂不混入A股主线</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>华夏基金官网：可检索到产品代码513910</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>港股通红利低波</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>港股低波红利</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>华夏标普港股通低波红利ETF</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>159118</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>华夏基金</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>标普港股通低波红利相关指数</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n"/>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="n"/>
+      <c r="N60" s="2" t="n"/>
+      <c r="O60" s="2" t="n"/>
+      <c r="P60" s="2" t="n"/>
+      <c r="Q60" s="2" t="n"/>
+      <c r="R60" s="2" t="n"/>
+      <c r="S60" s="2" t="n"/>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别：跨境补充
+待校验事项：属于港股通/跨境方向，暂不混入A股主线</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>公开基金公告/产品资料：可检索到该产品线索</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:U1"/>
+  <autoFilter ref="A1:U60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/02_outputs/excel/境内策略ETF产品梳理_初版.xlsx
+++ b/02_outputs/excel/境内策略ETF产品梳理_初版.xlsx
@@ -12,7 +12,7 @@
     <sheet name="指数规则表" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'产品总表'!$A$1:$U$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'产品总表'!$A$1:$U$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'策略分类表'!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'指数规则表'!$A$1:$P$1</definedName>
   </definedNames>
@@ -72,12 +72,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -445,13 +448,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U60"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
@@ -466,9 +469,9 @@
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
-    <col width="42" customWidth="1" min="20" max="20"/>
-    <col width="42" customWidth="1" min="21" max="21"/>
+    <col width="44" customWidth="1" min="19" max="19"/>
+    <col width="44" customWidth="1" min="20" max="20"/>
+    <col width="44" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -594,7 +597,7 @@
           <t>华泰柏瑞上证红利ETF</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>510880</t>
         </is>
@@ -616,7 +619,11 @@
           <t>上证红利指数</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n"/>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>上证</t>
+        </is>
+      </c>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
@@ -624,11 +631,19 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>产品名称属于典型策略方向</t>
+        </is>
+      </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线</t>
+          <t>清洗备注：指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
@@ -653,7 +668,7 @@
           <t>招商中证红利ETF</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>515080</t>
         </is>
@@ -675,7 +690,11 @@
           <t>中证红利指数</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n"/>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
@@ -683,11 +702,15 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="n"/>
-      <c r="S3" s="2" t="n"/>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr"/>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线</t>
+          <t>清洗备注：指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
@@ -712,7 +735,7 @@
           <t>易方达中证红利ETF</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>515180</t>
         </is>
@@ -734,7 +757,11 @@
           <t>中证红利指数</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
@@ -742,11 +769,15 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="n"/>
       <c r="Q4" s="2" t="n"/>
-      <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2" t="n"/>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr"/>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线</t>
+          <t>清洗备注：指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -771,7 +802,7 @@
           <t>博时中证红利ETF</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>515890</t>
         </is>
@@ -793,7 +824,11 @@
           <t>中证红利指数</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n"/>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
@@ -801,12 +836,16 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="n"/>
       <c r="Q5" s="2" t="n"/>
-      <c r="R5" s="2" t="n"/>
-      <c r="S5" s="2" t="n"/>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr"/>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：规模/上市日期后续用Wind校验</t>
+          <t>待校验事项：规模/上市日期后续用Wind校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -831,7 +870,7 @@
           <t>汇添富中证红利ETF</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>560020</t>
         </is>
@@ -853,7 +892,11 @@
           <t>中证红利指数</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n"/>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
@@ -861,12 +904,16 @@
       <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="n"/>
       <c r="Q6" s="2" t="n"/>
-      <c r="R6" s="2" t="n"/>
-      <c r="S6" s="2" t="n"/>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr"/>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：规模/上市日期后续用Wind校验</t>
+          <t>待校验事项：规模/上市日期后续用Wind校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -891,7 +938,7 @@
           <t>广发中证红利ETF</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>159589</t>
         </is>
@@ -913,7 +960,11 @@
           <t>中证红利指数</t>
         </is>
       </c>
-      <c r="J7" s="2" t="n"/>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
@@ -921,12 +972,16 @@
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="n"/>
       <c r="Q7" s="2" t="n"/>
-      <c r="R7" s="2" t="n"/>
-      <c r="S7" s="2" t="n"/>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr"/>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：规模/上市日期后续用Wind校验</t>
+          <t>待校验事项：规模/上市日期后续用Wind校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -951,7 +1006,7 @@
           <t>万家中证红利ETF</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>159581</t>
         </is>
@@ -973,7 +1028,11 @@
           <t>中证红利指数</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n"/>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
@@ -981,12 +1040,16 @@
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="n"/>
-      <c r="R8" s="2" t="n"/>
-      <c r="S8" s="2" t="n"/>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr"/>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：规模/上市日期后续用Wind校验</t>
+          <t>待校验事项：规模/上市日期后续用Wind校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1011,7 +1074,7 @@
           <t>工银深证红利ETF</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>159905</t>
         </is>
@@ -1033,7 +1096,11 @@
           <t>深证红利股票指数</t>
         </is>
       </c>
-      <c r="J9" s="2" t="n"/>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>深证</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
@@ -1041,11 +1108,15 @@
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="n"/>
       <c r="Q9" s="2" t="n"/>
-      <c r="R9" s="2" t="n"/>
-      <c r="S9" s="2" t="n"/>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr"/>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线</t>
+          <t>清洗备注：指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1070,7 +1141,7 @@
           <t>西部利得深证红利ETF</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>159708</t>
         </is>
@@ -1092,7 +1163,11 @@
           <t>深证红利指数</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>深证</t>
+        </is>
+      </c>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
       <c r="M10" s="2" t="n"/>
@@ -1100,12 +1175,16 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="n"/>
       <c r="Q10" s="2" t="n"/>
-      <c r="R10" s="2" t="n"/>
-      <c r="S10" s="2" t="n"/>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr"/>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：规模/上市日期后续用Wind校验</t>
+          <t>待校验事项：规模/上市日期后续用Wind校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1117,7 +1196,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>高股息</t>
+          <t>红利</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1130,7 +1209,7 @@
           <t>广发中证智选高股息策略ETF</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>159207</t>
         </is>
@@ -1152,7 +1231,11 @@
           <t>中证智选高股息策略指数</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
@@ -1160,12 +1243,16 @@
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="n"/>
       <c r="Q11" s="2" t="n"/>
-      <c r="R11" s="2" t="n"/>
-      <c r="S11" s="2" t="n"/>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr"/>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：新产品需校验规模与上市日期</t>
+          <t>待校验事项：新产品需校验规模与上市日期
+清洗备注：策略大类由高股息标准化为红利；标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1190,7 +1277,7 @@
           <t>华泰柏瑞中证红利低波动ETF</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>512890</t>
         </is>
@@ -1212,7 +1299,11 @@
           <t>中证红利低波动指数</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
@@ -1220,11 +1311,19 @@
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="n"/>
       <c r="Q12" s="2" t="n"/>
-      <c r="R12" s="2" t="n"/>
-      <c r="S12" s="2" t="n"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>原始标记为主线重点；产品名称属于典型策略方向</t>
+        </is>
+      </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线重点</t>
+          <t>清洗备注：纳入级别由主线重点标准化为主线；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1249,7 +1348,7 @@
           <t>景顺长城中证红利低波动100ETF</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>515100</t>
         </is>
@@ -1271,7 +1370,11 @@
           <t>中证红利低波动100指数</t>
         </is>
       </c>
-      <c r="J13" s="2" t="n"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
@@ -1279,11 +1382,19 @@
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="n"/>
       <c r="Q13" s="2" t="n"/>
-      <c r="R13" s="2" t="n"/>
-      <c r="S13" s="2" t="n"/>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>原始标记为主线重点</t>
+        </is>
+      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线重点</t>
+          <t>清洗备注：纳入级别由主线重点标准化为主线；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1308,7 +1419,7 @@
           <t>嘉实沪深300红利低波动ETF</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>515300</t>
         </is>
@@ -1330,7 +1441,11 @@
           <t>沪深300红利低波动指数</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
       <c r="M14" s="2" t="n"/>
@@ -1338,12 +1453,16 @@
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="n"/>
       <c r="Q14" s="2" t="n"/>
-      <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2" t="n"/>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr"/>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：规模/上市日期后续用Wind校验</t>
+          <t>待校验事项：规模/上市日期后续用Wind校验
+清洗备注：标记为待校验；指数公司待补充</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1368,7 +1487,7 @@
           <t>南方标普中国A股大盘红利低波50ETF</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>515450</t>
         </is>
@@ -1390,7 +1509,11 @@
           <t>标普中国A股大盘红利低波50指数</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>标普</t>
+        </is>
+      </c>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
       <c r="M15" s="2" t="n"/>
@@ -1398,11 +1521,19 @@
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="n"/>
       <c r="Q15" s="2" t="n"/>
-      <c r="R15" s="2" t="n"/>
-      <c r="S15" s="2" t="n"/>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>原始标记为主线重点</t>
+        </is>
+      </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线重点</t>
+          <t>清洗备注：纳入级别由主线重点标准化为主线；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -1427,7 +1558,7 @@
           <t>平安中证A500红利低波动ETF</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>561680</t>
         </is>
@@ -1449,7 +1580,11 @@
           <t>中证A500红利低波动指数</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n"/>
@@ -1457,12 +1592,16 @@
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="n"/>
       <c r="Q16" s="2" t="n"/>
-      <c r="R16" s="2" t="n"/>
-      <c r="S16" s="2" t="n"/>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr"/>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：新产品需校验规模/上市日期</t>
+          <t>待校验事项：新产品需校验规模/上市日期
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -1487,7 +1626,7 @@
           <t>易方达中证A500红利低波动ETF</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>563510</t>
         </is>
@@ -1509,7 +1648,11 @@
           <t>中证A500红利低波动指数</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n"/>
@@ -1517,12 +1660,16 @@
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="n"/>
       <c r="Q17" s="2" t="n"/>
-      <c r="R17" s="2" t="n"/>
-      <c r="S17" s="2" t="n"/>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr"/>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：新产品需校验规模/上市日期</t>
+          <t>待校验事项：新产品需校验规模/上市日期
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -1547,7 +1694,7 @@
           <t>A500红利低波ETF</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>159296</t>
         </is>
@@ -1569,7 +1716,11 @@
           <t>中证A500红利低波动指数</t>
         </is>
       </c>
-      <c r="J18" s="2" t="n"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n"/>
@@ -1577,12 +1728,16 @@
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
-      <c r="R18" s="2" t="n"/>
-      <c r="S18" s="2" t="n"/>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr"/>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：管理人和产品全称待Wind校验</t>
+          <t>待校验事项：管理人和产品全称待Wind校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -1607,7 +1762,7 @@
           <t>博时中证红利低波100ETF</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>159307</t>
         </is>
@@ -1629,7 +1784,11 @@
           <t>中证红利低波动100指数</t>
         </is>
       </c>
-      <c r="J19" s="2" t="n"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n"/>
@@ -1637,12 +1796,16 @@
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="n"/>
       <c r="Q19" s="2" t="n"/>
-      <c r="R19" s="2" t="n"/>
-      <c r="S19" s="2" t="n"/>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr"/>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：基金全称/规模/上市日期需Wind校验</t>
+          <t>待校验事项：基金全称/规模/上市日期需Wind校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -1667,7 +1830,7 @@
           <t>华安沪深300行业中性低波ETF</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>512270</t>
         </is>
@@ -1689,7 +1852,11 @@
           <t>沪深300行业中性低波动指数</t>
         </is>
       </c>
-      <c r="J20" s="2" t="n"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
@@ -1697,11 +1864,15 @@
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
-      <c r="R20" s="2" t="n"/>
-      <c r="S20" s="2" t="n"/>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr"/>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线</t>
+          <t>清洗备注：指数公司待补充</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -1726,7 +1897,7 @@
           <t>华安中证500行业中性低波ETF</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>512260</t>
         </is>
@@ -1748,7 +1919,11 @@
           <t>中证500行业中性低波动指数</t>
         </is>
       </c>
-      <c r="J21" s="2" t="n"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="2" t="n"/>
@@ -1756,11 +1931,15 @@
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
-      <c r="R21" s="2" t="n"/>
-      <c r="S21" s="2" t="n"/>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr"/>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线</t>
+          <t>清洗备注：指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -1785,7 +1964,7 @@
           <t>华夏国证自由现金流ETF</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>159201</t>
         </is>
@@ -1807,7 +1986,11 @@
           <t>国证自由现金流指数</t>
         </is>
       </c>
-      <c r="J22" s="2" t="n"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>国证</t>
+        </is>
+      </c>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n"/>
@@ -1815,12 +1998,20 @@
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="n"/>
       <c r="Q22" s="2" t="n"/>
-      <c r="R22" s="2" t="n"/>
-      <c r="S22" s="2" t="n"/>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>原始标记为主线重点；产品名称属于典型策略方向</t>
+        </is>
+      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线重点
-待校验事项：新产品需校验规模/上市日期</t>
+          <t>待校验事项：新产品需校验规模/上市日期
+清洗备注：纳入级别由主线重点标准化为主线；标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -1845,7 +2036,7 @@
           <t>易方达国证自由现金流ETF</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>159222</t>
         </is>
@@ -1867,7 +2058,11 @@
           <t>国证自由现金流指数</t>
         </is>
       </c>
-      <c r="J23" s="2" t="n"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>国证</t>
+        </is>
+      </c>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n"/>
@@ -1875,12 +2070,20 @@
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="n"/>
       <c r="Q23" s="2" t="n"/>
-      <c r="R23" s="2" t="n"/>
-      <c r="S23" s="2" t="n"/>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>原始标记为主线重点；产品名称属于典型策略方向</t>
+        </is>
+      </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线重点
-待校验事项：新产品需校验规模/上市日期</t>
+          <t>待校验事项：新产品需校验规模/上市日期
+清洗备注：纳入级别由主线重点标准化为主线；标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -1897,21 +2100,41 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>富时规模/上市日期</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr"/>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>易方达基金官网：显示代码159222、深交所上市、标的指数为国证自由现金流指数</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr"/>
-      <c r="F24" s="2" t="inlineStr"/>
+          <t>富时自由现金流聚焦</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>国泰富时中国A股自由现金流聚焦ETF</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>159399</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>国泰基金</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>深交所</t>
+        </is>
+      </c>
       <c r="G24" s="2" t="n"/>
       <c r="H24" s="2" t="n"/>
-      <c r="I24" s="2" t="inlineStr"/>
-      <c r="J24" s="2" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>富时中国A股自由现金流聚焦指数</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>富时罗素</t>
+        </is>
+      </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
       <c r="M24" s="2" t="n"/>
@@ -1919,14 +2142,23 @@
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="n"/>
       <c r="Q24" s="2" t="n"/>
-      <c r="R24" s="2" t="n"/>
-      <c r="S24" s="2" t="n"/>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr"/>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr"/>
+          <t>待校验事项：指数细节和上市日期需Wind校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>公开资料：显示其属于自由现金流聚焦方向</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1936,22 +2168,22 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>富时自由现金流聚焦</t>
+          <t>自由现金流</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>国泰富时中国A股自由现金流聚焦ETF</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>159399</t>
+          <t>广发自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>159229</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>国泰基金</t>
+          <t>广发基金</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1963,10 +2195,14 @@
       <c r="H25" s="2" t="n"/>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>富时中国A股自由现金流聚焦指数</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="n"/>
+          <t>自由现金流相关指数</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n"/>
@@ -1974,17 +2210,25 @@
       <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="n"/>
       <c r="Q25" s="2" t="n"/>
-      <c r="R25" s="2" t="n"/>
-      <c r="S25" s="2" t="n"/>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>产品名称属于典型策略方向</t>
+        </is>
+      </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：指数细节和上市日期需Wind校验</t>
+          <t>待校验事项：跟踪指数全称需Wind校验
+清洗备注：标记为待校验；指数公司待补充</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>公开资料：显示其属于自由现金流聚焦方向</t>
+          <t>天天基金/基金F10：可检索到自由现金流ETF广发159229</t>
         </is>
       </c>
     </row>
@@ -2001,17 +2245,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>广发自由现金流ETF</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>159229</t>
+          <t>工银自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>159236</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>广发基金</t>
+          <t>工银瑞信</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2026,7 +2270,11 @@
           <t>自由现金流相关指数</t>
         </is>
       </c>
-      <c r="J26" s="2" t="n"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="n"/>
       <c r="M26" s="2" t="n"/>
@@ -2034,17 +2282,25 @@
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="n"/>
       <c r="Q26" s="2" t="n"/>
-      <c r="R26" s="2" t="n"/>
-      <c r="S26" s="2" t="n"/>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>产品名称属于典型策略方向</t>
+        </is>
+      </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：跟踪指数全称需Wind校验</t>
+          <t>待校验事项：跟踪指数全称需Wind校验
+清洗备注：标记为待校验；指数公司待补充</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>天天基金/基金F10：可检索到自由现金流ETF广发159229</t>
+          <t>天天基金/基金F10：可检索到自由现金流ETF工银159236</t>
         </is>
       </c>
     </row>
@@ -2056,22 +2312,22 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>自由现金流</t>
+          <t>中证全指自由现金流</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>工银自由现金流ETF</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>159236</t>
+          <t>平安中证全指自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>159233</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>工银瑞信</t>
+          <t>平安基金</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -2083,10 +2339,14 @@
       <c r="H27" s="2" t="n"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>自由现金流相关指数</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="n"/>
+          <t>中证全指自由现金流指数</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="n"/>
       <c r="M27" s="2" t="n"/>
@@ -2094,17 +2354,25 @@
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="n"/>
       <c r="Q27" s="2" t="n"/>
-      <c r="R27" s="2" t="n"/>
-      <c r="S27" s="2" t="n"/>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>产品名称属于典型策略方向</t>
+        </is>
+      </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：跟踪指数全称需Wind校验</t>
+          <t>待校验事项：新产品需校验规模/上市日期
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>天天基金/基金F10：可检索到自由现金流ETF工银159236</t>
+          <t>平安基金官网：显示代码159233，标的指数为中证全指自由现金流指数</t>
         </is>
       </c>
     </row>
@@ -2121,22 +2389,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>平安中证全指自由现金流ETF</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>159233</t>
+          <t>兴业中证全指自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>563620</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>平安基金</t>
+          <t>兴业基金</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="G28" s="2" t="n"/>
@@ -2146,7 +2414,11 @@
           <t>中证全指自由现金流指数</t>
         </is>
       </c>
-      <c r="J28" s="2" t="n"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="2" t="n"/>
@@ -2154,17 +2426,25 @@
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="n"/>
       <c r="Q28" s="2" t="n"/>
-      <c r="R28" s="2" t="n"/>
-      <c r="S28" s="2" t="n"/>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>产品名称属于典型策略方向</t>
+        </is>
+      </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：新产品需校验规模/上市日期</t>
+          <t>待校验事项：新产品需校验规模/上市日期
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>平安基金官网：显示代码159233，标的指数为中证全指自由现金流指数</t>
+          <t>兴业基金官网：显示产品代码563620，法定名称为兴业中证全指自由现金流ETF</t>
         </is>
       </c>
     </row>
@@ -2176,37 +2456,41 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>中证全指自由现金流</t>
+          <t>国证自由现金流</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>兴业中证全指自由现金流ETF</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>563620</t>
+          <t>银华国证自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>待校验</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>兴业基金</t>
+          <t>银华基金</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>待校验</t>
         </is>
       </c>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="n"/>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>中证全指自由现金流指数</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="n"/>
+          <t>国证自由现金流指数</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>国证</t>
+        </is>
+      </c>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
@@ -2214,17 +2498,25 @@
       <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n"/>
-      <c r="R29" s="2" t="n"/>
-      <c r="S29" s="2" t="n"/>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>产品名称属于典型策略方向</t>
+        </is>
+      </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：新产品需校验规模/上市日期</t>
+          <t>待校验事项：公开搜索主要找到联接基金，目标ETF代码需Wind校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>兴业基金官网：显示产品代码563620，法定名称为兴业中证全指自由现金流ETF</t>
+          <t>天天基金/基金F10：可检索到银华国证自由现金流联接基金线索</t>
         </is>
       </c>
     </row>
@@ -2241,17 +2533,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>银华国证自由现金流ETF</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+          <t>永赢国证自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>待校验</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>银华基金</t>
+          <t>永赢基金</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2266,7 +2558,11 @@
           <t>国证自由现金流指数</t>
         </is>
       </c>
-      <c r="J30" s="2" t="n"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>国证</t>
+        </is>
+      </c>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
@@ -2274,17 +2570,25 @@
       <c r="O30" s="2" t="n"/>
       <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="n"/>
-      <c r="R30" s="2" t="n"/>
-      <c r="S30" s="2" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>产品名称属于典型策略方向</t>
+        </is>
+      </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：仅作线索
-待校验事项：公开搜索主要找到联接基金，目标ETF代码需Wind校验</t>
+          <t>待校验事项：公开搜索主要找到联接基金，目标ETF代码需Wind校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>天天基金/基金F10：可检索到银华国证自由现金流联接基金线索</t>
+          <t>天天基金/基金F10：可检索到永赢国证自由现金流联接基金线索</t>
         </is>
       </c>
     </row>
@@ -2301,17 +2605,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>永赢国证自由现金流ETF</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+          <t>长城国证自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
         <is>
           <t>待校验</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>永赢基金</t>
+          <t>长城基金</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2326,7 +2630,11 @@
           <t>国证自由现金流指数</t>
         </is>
       </c>
-      <c r="J31" s="2" t="n"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>国证</t>
+        </is>
+      </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
@@ -2334,59 +2642,71 @@
       <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
-      <c r="R31" s="2" t="n"/>
-      <c r="S31" s="2" t="n"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>产品名称属于典型策略方向</t>
+        </is>
+      </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：仅作线索
-待校验事项：公开搜索主要找到联接基金，目标ETF代码需Wind校验</t>
+          <t>待校验事项：公开搜索主要找到联接基金，目标ETF代码需Wind校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>天天基金/基金F10：可检索到永赢国证自由现金流联接基金线索</t>
+          <t>长城基金官网/公开基金页面：可检索到国证自由现金流联接基金线索</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>自由现金流</t>
+          <t>质量</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>国证自由现金流</t>
+          <t>红利质量</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>长城国证自由现金流ETF</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>待校验</t>
+          <t>华夏中证红利质量ETF</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>159758</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>长城基金</t>
+          <t>华夏基金</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待校验</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="G32" s="2" t="n"/>
       <c r="H32" s="2" t="n"/>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>国证自由现金流指数</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="n"/>
+          <t>中证红利质量指数</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
@@ -2394,17 +2714,20 @@
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="n"/>
-      <c r="R32" s="2" t="n"/>
-      <c r="S32" s="2" t="n"/>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：仅作线索
-待校验事项：公开搜索主要找到联接基金，目标ETF代码需Wind校验</t>
+          <t>清洗备注：指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>长城基金官网/公开基金页面：可检索到国证自由现金流联接基金线索</t>
+          <t>华夏基金官网：显示代码159758、基金全称为华夏中证红利质量ETF</t>
         </is>
       </c>
     </row>
@@ -2421,17 +2744,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>华夏中证红利质量ETF</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>159758</t>
+          <t>招商中证全指红利质量ETF</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>159209</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>华夏基金</t>
+          <t>招商基金</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2443,10 +2766,14 @@
       <c r="H33" s="2" t="n"/>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>中证红利质量指数</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="n"/>
+          <t>中证全指红利质量指数</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="2" t="n"/>
@@ -2454,16 +2781,21 @@
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="n"/>
       <c r="Q33" s="2" t="n"/>
-      <c r="R33" s="2" t="n"/>
-      <c r="S33" s="2" t="n"/>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr"/>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线</t>
+          <t>待校验事项：新产品需校验规模/上市日期
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>华夏基金官网：显示代码159758、基金全称为华夏中证红利质量ETF</t>
+          <t>天天基金/招商公告：可检索到红利质量ETF招商159209</t>
         </is>
       </c>
     </row>
@@ -2480,22 +2812,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>招商中证全指红利质量ETF</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>159209</t>
+          <t>易方达中证全指红利质量ETF</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>560370</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>招商基金</t>
+          <t>易方达</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="G34" s="2" t="n"/>
@@ -2505,7 +2837,11 @@
           <t>中证全指红利质量指数</t>
         </is>
       </c>
-      <c r="J34" s="2" t="n"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
@@ -2513,44 +2849,48 @@
       <c r="O34" s="2" t="n"/>
       <c r="P34" s="2" t="n"/>
       <c r="Q34" s="2" t="n"/>
-      <c r="R34" s="2" t="n"/>
-      <c r="S34" s="2" t="n"/>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr"/>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：新产品需校验规模/上市日期</t>
+          <t>待校验事项：新产品需校验规模/上市日期
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>天天基金/招商公告：可检索到红利质量ETF招商159209</t>
+          <t>易方达基金官网：可检索到产品代码560370</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>质量</t>
+          <t>价值</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>红利质量</t>
+          <t>价值因子</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>易方达中证全指红利质量ETF</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>560370</t>
+          <t>富国中证价值ETF</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>512040</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>易方达</t>
+          <t>富国基金</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2562,10 +2902,14 @@
       <c r="H35" s="2" t="n"/>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>中证全指红利质量指数</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="n"/>
+          <t>中证价值相关指数</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n"/>
@@ -2573,17 +2917,25 @@
       <c r="O35" s="2" t="n"/>
       <c r="P35" s="2" t="n"/>
       <c r="Q35" s="2" t="n"/>
-      <c r="R35" s="2" t="n"/>
-      <c r="S35" s="2" t="n"/>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>产品名称属于典型策略方向</t>
+        </is>
+      </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：新产品需校验规模/上市日期</t>
+          <t>待校验事项：跟踪指数全称需校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>易方达基金官网：可检索到产品代码560370</t>
+          <t>富国基金官网：显示基金名称为富国中证价值ETF，代码512040</t>
         </is>
       </c>
     </row>
@@ -2595,37 +2947,41 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>价值因子</t>
+          <t>国证价值100</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>富国中证价值ETF</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>512040</t>
+          <t>易方达国证价值100ETF</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>159263</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>富国基金</t>
+          <t>易方达</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="n"/>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>中证价值相关指数</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="n"/>
+          <t>国证价值100指数</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>国证</t>
+        </is>
+      </c>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
@@ -2633,44 +2989,48 @@
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="n"/>
       <c r="Q36" s="2" t="n"/>
-      <c r="R36" s="2" t="n"/>
-      <c r="S36" s="2" t="n"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr"/>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：跟踪指数全称需校验</t>
+          <t>待校验事项：新产品需校验规模/上市日期
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>富国基金官网：显示基金名称为富国中证价值ETF，代码512040</t>
+          <t>易方达基金官网：显示代码159263，基金名称为易方达国证价值100ETF</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>价值</t>
+          <t>成长</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>国证价值100</t>
+          <t>创业板动量成长</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>易方达国证价值100ETF</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>159263</t>
+          <t>华夏创业板动量成长ETF</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>159967</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>易方达</t>
+          <t>华夏基金</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -2682,10 +3042,14 @@
       <c r="H37" s="2" t="n"/>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>国证价值100指数</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n"/>
+          <t>创业板动量成长指数/创成长指数</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
       <c r="M37" s="2" t="n"/>
@@ -2693,17 +3057,21 @@
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="n"/>
       <c r="Q37" s="2" t="n"/>
-      <c r="R37" s="2" t="n"/>
-      <c r="S37" s="2" t="n"/>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr"/>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：新产品需校验规模/上市日期</t>
+          <t>待校验事项：指数简称和全称需Wind校验
+清洗备注：标记为待校验；指数公司待补充</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>易方达基金官网：显示代码159263，基金名称为易方达国证价值100ETF</t>
+          <t>天天基金/基金F10：可检索到创业板成长ETF华夏159967</t>
         </is>
       </c>
     </row>
@@ -2715,22 +3083,22 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>创业板动量成长</t>
+          <t>深证成长40</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>华夏创业板动量成长ETF</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>159967</t>
+          <t>大成深证成长40ETF</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>159906</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>华夏基金</t>
+          <t>大成基金</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2742,10 +3110,14 @@
       <c r="H38" s="2" t="n"/>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>创业板动量成长指数/创成长指数</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n"/>
+          <t>深证成长40指数</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>深证</t>
+        </is>
+      </c>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="2" t="n"/>
@@ -2753,17 +3125,20 @@
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="n"/>
       <c r="Q38" s="2" t="n"/>
-      <c r="R38" s="2" t="n"/>
-      <c r="S38" s="2" t="n"/>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr"/>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：指数简称和全称需Wind校验</t>
+          <t>清洗备注：指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>天天基金/基金F10：可检索到创业板成长ETF华夏159967</t>
+          <t>天天基金/基金F10：显示基金全称为深证成长40交易型开放式指数基金</t>
         </is>
       </c>
     </row>
@@ -2775,37 +3150,41 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>深证成长40</t>
+          <t>科创成长</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>大成深证成长40ETF</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>159906</t>
+          <t>易方达上证科创板成长ETF</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>588020</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>大成基金</t>
+          <t>易方达</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="n"/>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>深证成长40指数</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="n"/>
+          <t>上证科创板成长指数</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>上证</t>
+        </is>
+      </c>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
@@ -2813,16 +3192,20 @@
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="n"/>
       <c r="Q39" s="2" t="n"/>
-      <c r="R39" s="2" t="n"/>
-      <c r="S39" s="2" t="n"/>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr"/>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线</t>
+          <t>清洗备注：指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>天天基金/基金F10：显示基金全称为深证成长40交易型开放式指数基金</t>
+          <t>易方达基金官网：说明该指数从科创板中选取营收与净利润等业绩指标增长率较高的50只证券</t>
         </is>
       </c>
     </row>
@@ -2839,17 +3222,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>易方达上证科创板成长ETF</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>588020</t>
+          <t>万家上证科创板成长ETF</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>588070</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>易方达</t>
+          <t>万家基金</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2864,7 +3247,11 @@
           <t>上证科创板成长指数</t>
         </is>
       </c>
-      <c r="J40" s="2" t="n"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>上证</t>
+        </is>
+      </c>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="2" t="n"/>
@@ -2872,16 +3259,20 @@
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="n"/>
       <c r="Q40" s="2" t="n"/>
-      <c r="R40" s="2" t="n"/>
-      <c r="S40" s="2" t="n"/>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr"/>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线</t>
+          <t>清洗备注：指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>易方达基金官网：说明该指数从科创板中选取营收与净利润等业绩指标增长率较高的50只证券</t>
+          <t>万家基金官网：显示标的指数为上证科创板成长指数</t>
         </is>
       </c>
     </row>
@@ -2898,17 +3289,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>万家上证科创板成长ETF</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>588070</t>
+          <t>南方上证科创板成长ETF</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>589700</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>万家基金</t>
+          <t>南方基金</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2923,7 +3314,11 @@
           <t>上证科创板成长指数</t>
         </is>
       </c>
-      <c r="J41" s="2" t="n"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>上证</t>
+        </is>
+      </c>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
       <c r="M41" s="2" t="n"/>
@@ -2931,16 +3326,21 @@
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="n"/>
       <c r="Q41" s="2" t="n"/>
-      <c r="R41" s="2" t="n"/>
-      <c r="S41" s="2" t="n"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr"/>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线</t>
+          <t>待校验事项：规模/上市日期后续用Wind校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>万家基金官网：显示标的指数为上证科创板成长指数</t>
+          <t>南方基金官网/上交所公告：可检索到代码589700</t>
         </is>
       </c>
     </row>
@@ -2957,17 +3357,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>南方上证科创板成长ETF</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>589700</t>
+          <t>广发上证科创板成长ETF</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>588110</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>南方基金</t>
+          <t>广发基金</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2982,7 +3382,11 @@
           <t>上证科创板成长指数</t>
         </is>
       </c>
-      <c r="J42" s="2" t="n"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>上证</t>
+        </is>
+      </c>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
       <c r="M42" s="2" t="n"/>
@@ -2990,44 +3394,47 @@
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="n"/>
       <c r="Q42" s="2" t="n"/>
-      <c r="R42" s="2" t="n"/>
-      <c r="S42" s="2" t="n"/>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S42" s="2" t="inlineStr"/>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线
-待校验事项：规模/上市日期后续用Wind校验</t>
+          <t>清洗备注：指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>南方基金官网/上交所公告：可检索到代码589700</t>
+          <t>广发基金官网：显示代码588110，基金名称为广发上证科创板成长ETF</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>成长</t>
+          <t>基本面策略</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>科创成长</t>
+          <t>基本面50</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>广发上证科创板成长ETF</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>588110</t>
+          <t>嘉实基本面50ETF</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>512750</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>广发基金</t>
+          <t>嘉实基金</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3039,10 +3446,14 @@
       <c r="H43" s="2" t="n"/>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>上证科创板成长指数</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="n"/>
+          <t>基本面50指数</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
       <c r="M43" s="2" t="n"/>
@@ -3050,16 +3461,24 @@
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="n"/>
       <c r="Q43" s="2" t="n"/>
-      <c r="R43" s="2" t="n"/>
-      <c r="S43" s="2" t="n"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>产品名称属于典型策略方向</t>
+        </is>
+      </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线</t>
+          <t>清洗备注：指数公司待补充</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>广发基金官网：显示代码588110，基金名称为广发上证科创板成长ETF</t>
+          <t>天天基金/基金F10：显示基本面50ETF嘉实为被动式指数化投资产品</t>
         </is>
       </c>
     </row>
@@ -3071,17 +3490,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>基本面50</t>
+          <t>深证基本面120</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>嘉实基本面50ETF</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>512750</t>
+          <t>嘉实深证基本面120ETF</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>159910</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -3091,17 +3510,21 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="G44" s="2" t="n"/>
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>基本面50指数</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="n"/>
+          <t>深证基本面120指数</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>深证</t>
+        </is>
+      </c>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
       <c r="M44" s="2" t="n"/>
@@ -3109,43 +3532,47 @@
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="n"/>
       <c r="Q44" s="2" t="n"/>
-      <c r="R44" s="2" t="n"/>
-      <c r="S44" s="2" t="n"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线</t>
+          <t>清洗备注：指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>天天基金/基金F10：显示基本面50ETF嘉实为被动式指数化投资产品</t>
+          <t>天天基金/基金F10：显示其以跟踪深证基本面120指数为原则</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>基本面策略</t>
+          <t>多因子/增强</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>深证基本面120</t>
+          <t>指数增强</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>嘉实深证基本面120ETF</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>159910</t>
+          <t>银华中证800增强ETF</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>159517</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>嘉实基金</t>
+          <t>银华基金</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -3157,10 +3584,14 @@
       <c r="H45" s="2" t="n"/>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>深证基本面120指数</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="n"/>
+          <t>中证800+指数增强</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K45" s="2" t="n"/>
       <c r="L45" s="2" t="n"/>
       <c r="M45" s="2" t="n"/>
@@ -3168,16 +3599,21 @@
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="n"/>
       <c r="Q45" s="2" t="n"/>
-      <c r="R45" s="2" t="n"/>
-      <c r="S45" s="2" t="n"/>
+      <c r="R45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr"/>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：主线</t>
+          <t>待校验事项：是否纳入策略ETF主线需问mentor
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>天天基金/基金F10：显示其以跟踪深证基本面120指数为原则</t>
+          <t>天天基金/基金F10：显示该产品采用指数增强投资策略，并使用多因子量化选股</t>
         </is>
       </c>
     </row>
@@ -3194,32 +3630,36 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>银华中证800增强ETF</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>159517</t>
+          <t>华夏中证A500增强策略ETF</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>512370</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>银华基金</t>
+          <t>华夏基金</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="G46" s="2" t="n"/>
       <c r="H46" s="2" t="n"/>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>中证800+指数增强</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="n"/>
+          <t>中证A500+增强策略</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="2" t="n"/>
@@ -3227,44 +3667,48 @@
       <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="n"/>
       <c r="Q46" s="2" t="n"/>
-      <c r="R46" s="2" t="n"/>
-      <c r="S46" s="2" t="n"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr"/>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：单列观察
-待校验事项：是否纳入策略ETF主线需问mentor</t>
+          <t>待校验事项：是否纳入策略ETF主线需问mentor
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>天天基金/基金F10：显示该产品采用指数增强投资策略，并使用多因子量化选股</t>
+          <t>华夏基金官网：可检索到代码512370</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>多因子/增强</t>
+          <t>央企股东回报</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>指数增强</t>
+          <t>央企股东回报</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>华夏中证A500增强策略ETF</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>512370</t>
+          <t>招商中证国新央企股东回报ETF</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>561960</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>华夏基金</t>
+          <t>招商基金</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -3276,10 +3720,14 @@
       <c r="H47" s="2" t="n"/>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>中证A500+增强策略</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="n"/>
+          <t>中证国新央企股东回报指数</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
       <c r="M47" s="2" t="n"/>
@@ -3287,17 +3735,21 @@
       <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="n"/>
       <c r="Q47" s="2" t="n"/>
-      <c r="R47" s="2" t="n"/>
-      <c r="S47" s="2" t="n"/>
+      <c r="R47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr"/>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：单列观察
-待校验事项：是否纳入策略ETF主线需问mentor</t>
+          <t>待校验事项：兼具央企主题和股东回报策略属性
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>华夏基金官网：可检索到代码512370</t>
+          <t>天天基金/基金F10：显示代码561960，跟踪中证国新央企股东回报指数</t>
         </is>
       </c>
     </row>
@@ -3314,17 +3766,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>招商中证国新央企股东回报ETF</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>561960</t>
+          <t>广发中证国新央企股东回报ETF</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>560700</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>招商基金</t>
+          <t>广发基金</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3339,7 +3791,11 @@
           <t>中证国新央企股东回报指数</t>
         </is>
       </c>
-      <c r="J48" s="2" t="n"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
       <c r="M48" s="2" t="n"/>
@@ -3347,17 +3803,21 @@
       <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="n"/>
       <c r="Q48" s="2" t="n"/>
-      <c r="R48" s="2" t="n"/>
-      <c r="S48" s="2" t="n"/>
+      <c r="R48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr"/>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：补充观察
-待校验事项：兼具央企主题和股东回报策略属性</t>
+          <t>待校验事项：兼具央企主题和股东回报策略属性
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>天天基金/基金F10：显示代码561960，跟踪中证国新央企股东回报指数</t>
+          <t>同花顺基金页面：显示代码560700、管理人为广发基金</t>
         </is>
       </c>
     </row>
@@ -3374,17 +3834,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>广发中证国新央企股东回报ETF</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>560700</t>
+          <t>汇添富中证国新央企股东回报ETF</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>560070</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>广发基金</t>
+          <t>汇添富</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3399,7 +3859,11 @@
           <t>中证国新央企股东回报指数</t>
         </is>
       </c>
-      <c r="J49" s="2" t="n"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K49" s="2" t="n"/>
       <c r="L49" s="2" t="n"/>
       <c r="M49" s="2" t="n"/>
@@ -3407,44 +3871,48 @@
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="n"/>
       <c r="Q49" s="2" t="n"/>
-      <c r="R49" s="2" t="n"/>
-      <c r="S49" s="2" t="n"/>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr"/>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：补充观察
-待校验事项：兼具央企主题和股东回报策略属性</t>
+          <t>待校验事项：兼具央企主题和股东回报策略属性
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>同花顺基金页面：显示代码560700、管理人为广发基金</t>
+          <t>汇添富基金官网：可检索到该产品，代码560070</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>央企股东回报</t>
+          <t>央企红利</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>央企股东回报</t>
+          <t>央企红利</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>汇添富中证国新央企股东回报ETF</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>560070</t>
+          <t>华泰柏瑞中证中央企业红利ETF</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>561580</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>汇添富</t>
+          <t>华泰柏瑞</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3456,10 +3924,14 @@
       <c r="H50" s="2" t="n"/>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>中证国新央企股东回报指数</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="n"/>
+          <t>中证央企红利指数</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K50" s="2" t="n"/>
       <c r="L50" s="2" t="n"/>
       <c r="M50" s="2" t="n"/>
@@ -3467,44 +3939,48 @@
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="n"/>
       <c r="Q50" s="2" t="n"/>
-      <c r="R50" s="2" t="n"/>
-      <c r="S50" s="2" t="n"/>
+      <c r="R50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr"/>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：补充观察
-待校验事项：兼具央企主题和股东回报策略属性</t>
+          <t>待校验事项：红利策略与央企主题交叉，是否纳入主线需问mentor
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>汇添富基金官网：可检索到该产品，代码560070</t>
+          <t>公开资料：显示该产品跟踪央企红利指数</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>央企红利</t>
+          <t>国企红利</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>央企红利</t>
+          <t>国企红利</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>华泰柏瑞中证中央企业红利ETF</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>561580</t>
+          <t>创金合信国企红利ETF</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>563890</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>华泰柏瑞</t>
+          <t>创金合信</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -3516,10 +3992,14 @@
       <c r="H51" s="2" t="n"/>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>中证央企红利指数</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="n"/>
+          <t>国企红利相关指数</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
       <c r="M51" s="2" t="n"/>
@@ -3527,17 +4007,21 @@
       <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="n"/>
       <c r="Q51" s="2" t="n"/>
-      <c r="R51" s="2" t="n"/>
-      <c r="S51" s="2" t="n"/>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr"/>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：补充观察
-待校验事项：红利策略与央企主题交叉，是否纳入主线需问mentor</t>
+          <t>待校验事项：指数名称/规模/上市日期需Wind校验
+清洗备注：标记为待校验；指数公司待补充</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>公开资料：显示该产品跟踪央企红利指数</t>
+          <t>天天基金/基金F10：可检索到该产品</t>
         </is>
       </c>
     </row>
@@ -3554,32 +4038,36 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>创金合信国企红利ETF</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>563890</t>
+          <t>国企红利ETF</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>159515</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>创金合信</t>
+          <t>待校验</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="G52" s="2" t="n"/>
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>国企红利相关指数</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="n"/>
+          <t>中证国有企业红利指数</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
       <c r="M52" s="2" t="n"/>
@@ -3587,17 +4075,21 @@
       <c r="O52" s="2" t="n"/>
       <c r="P52" s="2" t="n"/>
       <c r="Q52" s="2" t="n"/>
-      <c r="R52" s="2" t="n"/>
-      <c r="S52" s="2" t="n"/>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr"/>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：补充观察
-待校验事项：指数名称/规模/上市日期需Wind校验</t>
+          <t>待校验事项：管理人和产品全称待Wind校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>天天基金/基金F10：可检索到该产品</t>
+          <t>公开资料：显示159515跟踪中证国有企业红利指数</t>
         </is>
       </c>
     </row>
@@ -3614,32 +4106,36 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>国企红利ETF</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>159515</t>
+          <t>国泰上证国有企业红利ETF</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>510720</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>待校验</t>
+          <t>国泰基金</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="G53" s="2" t="n"/>
       <c r="H53" s="2" t="n"/>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>中证国有企业红利指数</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="n"/>
+          <t>上证国有企业红利相关指数</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>上证</t>
+        </is>
+      </c>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
       <c r="M53" s="2" t="n"/>
@@ -3647,44 +4143,48 @@
       <c r="O53" s="2" t="n"/>
       <c r="P53" s="2" t="n"/>
       <c r="Q53" s="2" t="n"/>
-      <c r="R53" s="2" t="n"/>
-      <c r="S53" s="2" t="n"/>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr"/>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：补充观察
-待校验事项：管理人和产品全称待Wind校验</t>
+          <t>待校验事项：指数名称/规模/上市日期需Wind校验
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>公开资料：显示159515跟踪中证国有企业红利指数</t>
+          <t>公开基金行情网站：可检索到基金名称、代码和管理人为国泰基金</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>国企红利</t>
+          <t>ESG</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>国企红利</t>
+          <t>180ESG</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>国泰上证国有企业红利ETF</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>510720</t>
+          <t>工银180ESGETF</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>510990</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>国泰基金</t>
+          <t>工银瑞信</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3696,10 +4196,14 @@
       <c r="H54" s="2" t="n"/>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>上证国有企业红利相关指数</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="n"/>
+          <t>ESG相关指数</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
       <c r="M54" s="2" t="n"/>
@@ -3707,17 +4211,21 @@
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="n"/>
       <c r="Q54" s="2" t="n"/>
-      <c r="R54" s="2" t="n"/>
-      <c r="S54" s="2" t="n"/>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr"/>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：补充观察
-待校验事项：指数名称/规模/上市日期需Wind校验</t>
+          <t>待校验事项：ESG是否作为主线需问mentor
+清洗备注：标记为待校验；指数公司待补充</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>公开基金行情网站：可检索到基金名称、代码和管理人为国泰基金</t>
+          <t>天天基金/基金F10：显示该产品采取完全复制策略，跟踪标的指数</t>
         </is>
       </c>
     </row>
@@ -3729,22 +4237,22 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>180ESG</t>
+          <t>央企ESG</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>工银180ESGETF</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>510990</t>
+          <t>融通中证诚通央企ESGETF</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>560810</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>工银瑞信</t>
+          <t>融通基金</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -3756,10 +4264,14 @@
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>ESG相关指数</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="n"/>
+          <t>中证诚通央企ESG指数</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
       <c r="M55" s="2" t="n"/>
@@ -3767,17 +4279,21 @@
       <c r="O55" s="2" t="n"/>
       <c r="P55" s="2" t="n"/>
       <c r="Q55" s="2" t="n"/>
-      <c r="R55" s="2" t="n"/>
-      <c r="S55" s="2" t="n"/>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr"/>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：补充观察
-待校验事项：ESG是否作为主线需问mentor</t>
+          <t>待校验事项：ESG是否作为主线需问mentor
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>天天基金/基金F10：显示该产品采取完全复制策略，跟踪标的指数</t>
+          <t>融通基金官网：显示产品为融通中证诚通央企ESGETF，代码560810</t>
         </is>
       </c>
     </row>
@@ -3789,22 +4305,22 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>央企ESG</t>
+          <t>可持续发展</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>融通中证诚通央企ESGETF</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>560810</t>
+          <t>博时中证可持续发展100ETF</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>515090</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>融通基金</t>
+          <t>博时基金</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -3816,10 +4332,14 @@
       <c r="H56" s="2" t="n"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>中证诚通央企ESG指数</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="n"/>
+          <t>中证可持续发展100指数</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
       <c r="K56" s="2" t="n"/>
       <c r="L56" s="2" t="n"/>
       <c r="M56" s="2" t="n"/>
@@ -3827,44 +4347,48 @@
       <c r="O56" s="2" t="n"/>
       <c r="P56" s="2" t="n"/>
       <c r="Q56" s="2" t="n"/>
-      <c r="R56" s="2" t="n"/>
-      <c r="S56" s="2" t="n"/>
+      <c r="R56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr"/>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：补充观察
-待校验事项：ESG是否作为主线需问mentor</t>
+          <t>待校验事项：ESG/可持续是否作为主线需问mentor
+清洗备注：策略大类由ESG/可持续标准化为ESG；标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>融通基金官网：显示产品为融通中证诚通央企ESGETF，代码560810</t>
+          <t>天天基金/基金F10：显示该产品跟踪中证可持续发展100指数</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ESG/可持续</t>
+          <t>港股通红利</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>可持续发展</t>
+          <t>港股通央企红利</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>博时中证可持续发展100ETF</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>515090</t>
+          <t>景顺长城中证国新港股通央企红利ETF</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>520990</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>博时基金</t>
+          <t>景顺长城</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -3876,10 +4400,14 @@
       <c r="H57" s="2" t="n"/>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>中证可持续发展100指数</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="n"/>
+          <t>港股通央企红利相关指数</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
       <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="n"/>
       <c r="M57" s="2" t="n"/>
@@ -3887,17 +4415,21 @@
       <c r="O57" s="2" t="n"/>
       <c r="P57" s="2" t="n"/>
       <c r="Q57" s="2" t="n"/>
-      <c r="R57" s="2" t="n"/>
-      <c r="S57" s="2" t="n"/>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr"/>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：补充观察
-待校验事项：ESG/可持续是否作为主线需问mentor</t>
+          <t>待校验事项：属于港股通/跨境方向，暂不混入A股主线
+清洗备注：标记为待校验；指数公司待补充</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>天天基金/基金F10：显示该产品跟踪中证可持续发展100指数</t>
+          <t>景顺长城基金官网：可检索到产品代码520990</t>
         </is>
       </c>
     </row>
@@ -3914,17 +4446,17 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>景顺长城中证国新港股通央企红利ETF</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>520990</t>
+          <t>华夏中证港股通央企红利ETF</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>513910</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>景顺长城</t>
+          <t>华夏基金</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -3939,7 +4471,11 @@
           <t>港股通央企红利相关指数</t>
         </is>
       </c>
-      <c r="J58" s="2" t="n"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="n"/>
       <c r="M58" s="2" t="n"/>
@@ -3947,39 +4483,43 @@
       <c r="O58" s="2" t="n"/>
       <c r="P58" s="2" t="n"/>
       <c r="Q58" s="2" t="n"/>
-      <c r="R58" s="2" t="n"/>
-      <c r="S58" s="2" t="n"/>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr"/>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：跨境补充
-待校验事项：属于港股通/跨境方向，暂不混入A股主线</t>
+          <t>待校验事项：属于港股通/跨境方向，暂不混入A股主线
+清洗备注：标记为待校验；指数公司待补充</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>景顺长城基金官网：可检索到产品代码520990</t>
+          <t>华夏基金官网：可检索到产品代码513910</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>港股通红利</t>
+          <t>港股通红利低波</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>港股通央企红利</t>
+          <t>港股低波红利</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>华夏中证港股通央企红利ETF</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>513910</t>
+          <t>华夏标普港股通低波红利ETF</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>159118</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3989,17 +4529,21 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="G59" s="2" t="n"/>
       <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>港股通央企红利相关指数</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="n"/>
+          <t>标普港股通低波红利相关指数</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>标普</t>
+        </is>
+      </c>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="2" t="n"/>
@@ -4007,82 +4551,26 @@
       <c r="O59" s="2" t="n"/>
       <c r="P59" s="2" t="n"/>
       <c r="Q59" s="2" t="n"/>
-      <c r="R59" s="2" t="n"/>
-      <c r="S59" s="2" t="n"/>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr"/>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>纳入级别：跨境补充
-待校验事项：属于港股通/跨境方向，暂不混入A股主线</t>
+          <t>待校验事项：属于港股通/跨境方向，暂不混入A股主线
+清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>华夏基金官网：可检索到产品代码513910</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>港股通红利低波</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>港股低波红利</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>华夏标普港股通低波红利ETF</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>159118</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>华夏基金</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>深交所</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="n"/>
-      <c r="H60" s="2" t="n"/>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>标普港股通低波红利相关指数</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="n"/>
-      <c r="K60" s="2" t="n"/>
-      <c r="L60" s="2" t="n"/>
-      <c r="M60" s="2" t="n"/>
-      <c r="N60" s="2" t="n"/>
-      <c r="O60" s="2" t="n"/>
-      <c r="P60" s="2" t="n"/>
-      <c r="Q60" s="2" t="n"/>
-      <c r="R60" s="2" t="n"/>
-      <c r="S60" s="2" t="n"/>
-      <c r="T60" s="2" t="inlineStr">
-        <is>
-          <t>纳入级别：跨境补充
-待校验事项：属于港股通/跨境方向，暂不混入A股主线</t>
-        </is>
-      </c>
-      <c r="U60" s="2" t="inlineStr">
-        <is>
           <t>公开基金公告/产品资料：可检索到该产品线索</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U60"/>
+  <autoFilter ref="A1:U59"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/02_outputs/excel/境内策略ETF产品梳理_初版.xlsx
+++ b/02_outputs/excel/境内策略ETF产品梳理_初版.xlsx
@@ -1443,7 +1443,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待补充</t>
+          <t>中证</t>
         </is>
       </c>
       <c r="K14" s="2" t="n"/>
@@ -1462,7 +1462,8 @@
       <c r="T14" s="2" t="inlineStr">
         <is>
           <t>待校验事项：规模/上市日期后续用Wind校验
-清洗备注：标记为待校验；指数公司待补充</t>
+清洗备注：标记为待校验；指数公司待补充
+Step 6 分类修正备注：只修正建议指数公司，策略分类不变</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1854,7 +1855,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待补充</t>
+          <t>中证</t>
         </is>
       </c>
       <c r="K20" s="2" t="n"/>
@@ -1872,7 +1873,8 @@
       <c r="S20" s="2" t="inlineStr"/>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>清洗备注：指数公司待补充</t>
+          <t>清洗备注：指数公司待补充
+Step 6 分类修正备注：只修正建议指数公司，策略分类不变</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2667,7 +2669,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>质量</t>
+          <t>红利质量</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2722,7 +2724,8 @@
       <c r="S32" s="2" t="inlineStr"/>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>清洗备注：指数公司由指数名称初步推断</t>
+          <t>清洗备注：指数公司由指数名称初步推断
+Step 6 分类修正备注：建议作为“红利+质量”复合策略单列，后续阅读指数规则确认红利因子与质量因子的筛选顺序</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -2734,7 +2737,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>质量</t>
+          <t>红利质量</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2790,7 +2793,8 @@
       <c r="T33" s="2" t="inlineStr">
         <is>
           <t>待校验事项：新产品需校验规模/上市日期
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step 6 分类修正备注：建议作为“红利+质量”复合策略单列，后续阅读指数规则确认样本空间和选样因子</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -2802,7 +2806,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>质量</t>
+          <t>红利质量</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2858,7 +2862,8 @@
       <c r="T34" s="2" t="inlineStr">
         <is>
           <t>待校验事项：新产品需校验规模/上市日期
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step 6 分类修正备注：建议作为“红利+质量”复合策略单列，后续阅读指数规则确认样本空间和选样因子</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -3552,7 +3557,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>多因子/增强</t>
+          <t>指数增强/多因子</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -3608,7 +3613,8 @@
       <c r="T45" s="2" t="inlineStr">
         <is>
           <t>待校验事项：是否纳入策略ETF主线需问mentor
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step 6 分类修正备注：后续需要和mentor确认指数增强ETF是否纳入策略ETF主线</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -3620,7 +3626,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>多因子/增强</t>
+          <t>指数增强/多因子</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -3676,7 +3682,8 @@
       <c r="T46" s="2" t="inlineStr">
         <is>
           <t>待校验事项：是否纳入策略ETF主线需问mentor
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step 6 分类修正备注：后续需要和mentor确认指数增强ETF是否纳入策略ETF主线</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -3688,7 +3695,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>央企股东回报</t>
+          <t>央国企红利/股东回报</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -3744,7 +3751,8 @@
       <c r="T47" s="2" t="inlineStr">
         <is>
           <t>待校验事项：兼具央企主题和股东回报策略属性
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step 6 分类修正备注：后续需要和mentor确认央企股东回报是否进入主线</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -3756,7 +3764,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>央企股东回报</t>
+          <t>央国企红利/股东回报</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -3812,7 +3820,8 @@
       <c r="T48" s="2" t="inlineStr">
         <is>
           <t>待校验事项：兼具央企主题和股东回报策略属性
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step 6 分类修正备注：后续需要和mentor确认央企股东回报是否进入主线</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -3824,7 +3833,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>央企股东回报</t>
+          <t>央国企红利/股东回报</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -3880,7 +3889,8 @@
       <c r="T49" s="2" t="inlineStr">
         <is>
           <t>待校验事项：兼具央企主题和股东回报策略属性
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step 6 分类修正备注：后续需要和mentor确认央企股东回报是否进入主线</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -3892,7 +3902,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>央企红利</t>
+          <t>央国企红利/股东回报</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -3948,7 +3958,8 @@
       <c r="T50" s="2" t="inlineStr">
         <is>
           <t>待校验事项：红利策略与央企主题交叉，是否纳入主线需问mentor
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step 6 分类修正备注：后续需要和mentor确认央企红利是否进入红利主线</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -3960,7 +3971,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>国企红利</t>
+          <t>央国企红利/股东回报</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -4016,7 +4027,8 @@
       <c r="T51" s="2" t="inlineStr">
         <is>
           <t>待校验事项：指数名称/规模/上市日期需Wind校验
-清洗备注：标记为待校验；指数公司待补充</t>
+清洗备注：标记为待校验；指数公司待补充
+Step 6 分类修正备注：跟踪指数名称仍为国企红利相关指数，需后续用Wind确认指数全称</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -4028,7 +4040,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>国企红利</t>
+          <t>央国企红利/股东回报</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -4084,7 +4096,8 @@
       <c r="T52" s="2" t="inlineStr">
         <is>
           <t>待校验事项：管理人和产品全称待Wind校验
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step 6 分类修正备注：产品全称和管理人仍需后续用Wind校验</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -4096,7 +4109,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>国企红利</t>
+          <t>央国企红利/股东回报</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -4152,7 +4165,8 @@
       <c r="T53" s="2" t="inlineStr">
         <is>
           <t>待校验事项：指数名称/规模/上市日期需Wind校验
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step 6 分类修正备注：跟踪指数全称仍需后续用Wind校验</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -4368,7 +4382,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>港股通红利</t>
+          <t>港股通红利/低波</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -4405,7 +4419,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>待补充</t>
+          <t>中证</t>
         </is>
       </c>
       <c r="K57" s="2" t="n"/>
@@ -4424,7 +4438,8 @@
       <c r="T57" s="2" t="inlineStr">
         <is>
           <t>待校验事项：属于港股通/跨境方向，暂不混入A股主线
-清洗备注：标记为待校验；指数公司待补充</t>
+清洗备注：标记为待校验；指数公司待补充
+Step 6 分类修正备注：后续需要和mentor确认港股通产品是否纳入境内部分</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -4436,7 +4451,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>港股通红利</t>
+          <t>港股通红利/低波</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -4473,7 +4488,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>待补充</t>
+          <t>中证</t>
         </is>
       </c>
       <c r="K58" s="2" t="n"/>
@@ -4492,7 +4507,8 @@
       <c r="T58" s="2" t="inlineStr">
         <is>
           <t>待校验事项：属于港股通/跨境方向，暂不混入A股主线
-清洗备注：标记为待校验；指数公司待补充</t>
+清洗备注：标记为待校验；指数公司待补充
+Step 6 分类修正备注：后续需要和mentor确认港股通产品是否纳入境内部分</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -4504,12 +4520,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>港股通红利低波</t>
+          <t>港股通红利/低波</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>港股低波红利</t>
+          <t>港股通低波红利</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4560,7 +4576,8 @@
       <c r="T59" s="2" t="inlineStr">
         <is>
           <t>待校验事项：属于港股通/跨境方向，暂不混入A股主线
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step 6 分类修正备注：后续需要和mentor确认港股通产品是否纳入境内部分</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">

--- a/02_outputs/excel/境内策略ETF产品梳理_初版.xlsx
+++ b/02_outputs/excel/境内策略ETF产品梳理_初版.xlsx
@@ -638,12 +638,13 @@
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>产品名称属于典型策略方向</t>
+          <t>境内传统红利ETF的经典代表，成立早、规模较大，适合作为上证红利策略样本</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>清洗备注：指数公司由指数名称初步推断</t>
+          <t>清洗备注：指数公司由指数名称初步推断
+Step7代表产品级别：核心代表；后续需看指数规则：样本空间、股息率筛选、成分数量、加权方式、调样频率</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
@@ -704,13 +705,18 @@
       <c r="Q3" s="2" t="n"/>
       <c r="R3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>代表中证红利指数体系，适合与上证红利、深证红利进行横向对比</t>
+        </is>
+      </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>清洗备注：指数公司由指数名称初步推断</t>
+          <t>清洗备注：指数公司由指数名称初步推断
+Step7代表产品级别：核心代表；后续需看指数规则：中证红利指数选样标准、股息率排序、权重限制</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
@@ -1110,13 +1116,18 @@
       <c r="Q9" s="2" t="n"/>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>代表深证红利风格，可与上证红利和中证红利形成交易所与市场板块对比</t>
+        </is>
+      </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>清洗备注：指数公司由指数名称初步推断</t>
+          <t>清洗备注：指数公司由指数名称初步推断
+Step7代表产品级别：核心代表；后续需看指数规则：深证红利指数样本空间、成长属性、行业分布</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1318,12 +1329,13 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>原始标记为主线重点；产品名称属于典型策略方向</t>
+          <t>红利低波方向最重要的代表产品之一，规模和市场认知度较高</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>清洗备注：纳入级别由主线重点标准化为主线；指数公司由指数名称初步推断</t>
+          <t>清洗备注：纳入级别由主线重点标准化为主线；指数公司由指数名称初步推断
+Step7代表产品级别：核心代表；后续需看指数规则：红利与低波筛选顺序、波动率计算方式、加权方式、权重限制</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1389,12 +1401,13 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>原始标记为主线重点</t>
+          <t>与512890同属红利低波，但成分数量和指数规则可能不同，适合对比</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>清洗备注：纳入级别由主线重点标准化为主线；指数公司由指数名称初步推断</t>
+          <t>清洗备注：纳入级别由主线重点标准化为主线；指数公司由指数名称初步推断
+Step7代表产品级别：核心代表；后续需看指数规则：成分数量、红利与低波筛选顺序、行业限制</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1524,7 +1537,7 @@
       <c r="Q15" s="2" t="n"/>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -1663,14 +1676,19 @@
       <c r="Q17" s="2" t="n"/>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>代表A500红利低波新方向，适合观察策略ETF如何嫁接新宽基指数生态</t>
+        </is>
+      </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
           <t>待校验事项：新产品需校验规模/上市日期
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step7代表产品级别：新方向代表；后续需看指数规则：A500样本空间、红利低波筛选、股息率加权、单只权重上限</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -1867,14 +1885,19 @@
       <c r="Q20" s="2" t="n"/>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>代表大盘低波策略，并加入行业中性约束，适合研究低波策略如何避免行业偏离</t>
+        </is>
+      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
           <t>清洗备注：指数公司待补充
-Step 6 分类修正备注：只修正建议指数公司，策略分类不变</t>
+Step 6 分类修正备注：只修正建议指数公司，策略分类不变
+Step7代表产品级别：核心代表；后续需看指数规则：低波指标、行业中性约束、波动率计算窗口、权重限制</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -1935,13 +1958,18 @@
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>代表中盘低波策略，与沪深300低波形成市值层面对比</t>
+        </is>
+      </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>清洗备注：指数公司由指数名称初步推断</t>
+          <t>清洗备注：指数公司由指数名称初步推断
+Step7代表产品级别：市值层面对比代表；后续需看指数规则：中证500样本空间、行业中性约束、低波筛选逻辑</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2007,13 +2035,14 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>原始标记为主线重点；产品名称属于典型策略方向</t>
+          <t>自由现金流方向的核心代表产品之一，适合重点分析现金创造能力策略</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
           <t>待校验事项：新产品需校验规模/上市日期
-清洗备注：纳入级别由主线重点标准化为主线；标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：纳入级别由主线重点标准化为主线；标记为待校验；指数公司由指数名称初步推断
+Step7代表产品级别：核心代表；后续需看指数规则：自由现金流率定义、选样池、行业约束、加权方式</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2079,13 +2108,14 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>原始标记为主线重点；产品名称属于典型策略方向</t>
+          <t>同样跟踪国证自由现金流指数，但基金公司代表性强，适合作为同指数多管理人竞争案例</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
           <t>待校验事项：新产品需校验规模/上市日期
-清洗备注：纳入级别由主线重点标准化为主线；标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：纳入级别由主线重点标准化为主线；标记为待校验；指数公司由指数名称初步推断
+Step7代表产品级别：核心代表；后续需看指数规则：同指数不同管理人产品的费率、规模、流动性差异</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2214,7 +2244,7 @@
       <c r="Q25" s="2" t="n"/>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -2286,7 +2316,7 @@
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -2363,13 +2393,14 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>产品名称属于典型策略方向</t>
+          <t>代表中证全指自由现金流指数体系，可与国证自由现金流进行规则对比</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
           <t>待校验事项：新产品需校验规模/上市日期
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step7代表产品级别：指数体系对比代表；后续需看指数规则：中证全指自由现金流指数选样因子、加权方式、行业分布</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -2430,7 +2461,7 @@
       <c r="Q28" s="2" t="n"/>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
@@ -2502,7 +2533,7 @@
       <c r="Q29" s="2" t="n"/>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -2574,7 +2605,7 @@
       <c r="Q30" s="2" t="n"/>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -2646,7 +2677,7 @@
       <c r="Q31" s="2" t="n"/>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -2718,14 +2749,19 @@
       <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>红利质量方向成立相对更早，适合作为红利+质量复合策略核心样本</t>
+        </is>
+      </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
           <t>清洗备注：指数公司由指数名称初步推断
-Step 6 分类修正备注：建议作为“红利+质量”复合策略单列，后续阅读指数规则确认红利因子与质量因子的筛选顺序</t>
+Step 6 分类修正备注：建议作为“红利+质量”复合策略单列，后续阅读指数规则确认红利因子与质量因子的筛选顺序
+Step7代表产品级别：核心代表；后续需看指数规则：红利因子和质量因子的筛选顺序、质量因子定义、权重方式</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -2786,15 +2822,20 @@
       <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>代表中证全指样本空间下的红利质量策略，可与159758比较</t>
+        </is>
+      </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
           <t>待校验事项：新产品需校验规模/上市日期
 清洗备注：标记为待校验；指数公司由指数名称初步推断
-Step 6 分类修正备注：建议作为“红利+质量”复合策略单列，后续阅读指数规则确认样本空间和选样因子</t>
+Step 6 分类修正备注：建议作为“红利+质量”复合策略单列，后续阅读指数规则确认样本空间和选样因子
+Step7代表产品级别：扩展代表；后续需看指数规则：中证全指红利质量指数样本空间、红利/质量打分方式</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -2929,13 +2970,14 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>产品名称属于典型策略方向</t>
+          <t>富国自身产品，且代表价值因子策略，应作为价值类重点样本</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
           <t>待校验事项：跟踪指数全称需校验
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step7代表产品级别：核心代表；后续需看指数规则：价值因子定义、估值指标、选样数量、权重方式</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -2996,14 +3038,19 @@
       <c r="Q36" s="2" t="n"/>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>代表国证价值指数体系，可与富国中证价值ETF进行指数公司和规则对比</t>
+        </is>
+      </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
           <t>待校验事项：新产品需校验规模/上市日期
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step7代表产品级别：指数体系对比代表；后续需看指数规则：低估值指标、盈利约束、成分数量</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -3064,14 +3111,19 @@
       <c r="Q37" s="2" t="n"/>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S37" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>代表成长+动量复合风格，区别于单纯成长因子</t>
+        </is>
+      </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
           <t>待校验事项：指数简称和全称需Wind校验
-清洗备注：标记为待校验；指数公司待补充</t>
+清洗备注：标记为待校验；指数公司待补充
+Step7代表产品级别：核心代表；后续需看指数规则：动量因子、成长因子、创业板样本空间、调样频率</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -3132,13 +3184,18 @@
       <c r="Q38" s="2" t="n"/>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S38" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>代表深证成长风格，适合观察早期成长策略指数规则</t>
+        </is>
+      </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>清洗备注：指数公司由指数名称初步推断</t>
+          <t>清洗备注：指数公司由指数名称初步推断
+Step7代表产品级别：经典代表；后续需看指数规则：成长指标、样本数量、权重方式</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -3199,13 +3256,18 @@
       <c r="Q39" s="2" t="n"/>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S39" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>代表科创板成长风格，适合观察成长策略与科创板主题池结合</t>
+        </is>
+      </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>清洗备注：指数公司由指数名称初步推断</t>
+          <t>清洗备注：指数公司由指数名称初步推断
+Step7代表产品级别：新经济成长代表；后续需看指数规则：科创板样本空间、营收增长、净利润增长、成分股数量</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -3473,12 +3535,13 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>产品名称属于典型策略方向</t>
+          <t>基本面加权类ETF的典型代表，适合分析非市值加权策略指数</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>清洗备注：指数公司待补充</t>
+          <t>清洗备注：指数公司待补充
+Step7代表产品级别：核心代表；后续需看指数规则：基本面指标、收入、现金流、净资产、分红、加权方式</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -3539,13 +3602,18 @@
       <c r="Q44" s="2" t="n"/>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>与基本面50形成数量和样本空间对比，适合观察深市基本面策略表达</t>
+        </is>
+      </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>清洗备注：指数公司由指数名称初步推断</t>
+          <t>清洗备注：指数公司由指数名称初步推断
+Step7代表产品级别：扩展代表；后续需看指数规则：深证基本面120指数基本面指标、成分数量、加权方式</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -3606,15 +3674,20 @@
       <c r="Q45" s="2" t="n"/>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>代表指数增强型ETF，适合单列观察，不建议和纯被动Smart Beta混在一起</t>
+        </is>
+      </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
           <t>待校验事项：是否纳入策略ETF主线需问mentor
 清洗备注：标记为待校验；指数公司由指数名称初步推断
-Step 6 分类修正备注：后续需要和mentor确认指数增强ETF是否纳入策略ETF主线</t>
+Step 6 分类修正备注：后续需要和mentor确认指数增强ETF是否纳入策略ETF主线
+Step7代表产品级别：单列观察代表；后续需看指数规则：增强模型是否披露、多因子框架、主动偏离约束</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -3675,15 +3748,20 @@
       <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>代表A500生态下的增强策略产品，适合观察指数增强和新宽基结合</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
           <t>待校验事项：是否纳入策略ETF主线需问mentor
 清洗备注：标记为待校验；指数公司由指数名称初步推断
-Step 6 分类修正备注：后续需要和mentor确认指数增强ETF是否纳入策略ETF主线</t>
+Step 6 分类修正备注：后续需要和mentor确认指数增强ETF是否纳入策略ETF主线
+Step7代表产品级别：单列观察代表；后续需看指数规则：增强策略边界、跟踪误差目标、主动风险约束</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -3744,15 +3822,20 @@
       <c r="Q47" s="2" t="n"/>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S47" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>体现央企主题与股东回报策略结合，适合作为中国特色策略ETF观察样本</t>
+        </is>
+      </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
           <t>待校验事项：兼具央企主题和股东回报策略属性
 清洗备注：标记为待校验；指数公司由指数名称初步推断
-Step 6 分类修正备注：后续需要和mentor确认央企股东回报是否进入主线</t>
+Step 6 分类修正备注：后续需要和mentor确认央企股东回报是否进入主线
+Step7代表产品级别：补充观察代表；后续需看指数规则：股东回报指标、央企样本空间、分红/回购/估值指标</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -3951,15 +4034,20 @@
       <c r="Q50" s="2" t="n"/>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S50" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>体现央企范围内的红利策略，属于红利策略的中国特色延伸</t>
+        </is>
+      </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
           <t>待校验事项：红利策略与央企主题交叉，是否纳入主线需问mentor
 清洗备注：标记为待校验；指数公司由指数名称初步推断
-Step 6 分类修正备注：后续需要和mentor确认央企红利是否进入红利主线</t>
+Step 6 分类修正备注：后续需要和mentor确认央企红利是否进入红利主线
+Step7代表产品级别：补充观察代表；后续需看指数规则：央企样本池、股息率筛选、行业集中度</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -4295,14 +4383,19 @@
       <c r="Q55" s="2" t="n"/>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>兼具央企主题和ESG评分逻辑，适合作为ESG策略观察样本</t>
+        </is>
+      </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
           <t>待校验事项：ESG是否作为主线需问mentor
-清洗备注：标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：标记为待校验；指数公司由指数名称初步推断
+Step7代表产品级别：补充观察代表；后续需看指数规则：ESG评分是否参与选样/加权、央企样本空间</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -4363,14 +4456,19 @@
       <c r="Q56" s="2" t="n"/>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>代表可持续发展策略方向，可作为ESG扩展样本</t>
+        </is>
+      </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
           <t>待校验事项：ESG/可持续是否作为主线需问mentor
-清洗备注：策略大类由ESG/可持续标准化为ESG；标记为待校验；指数公司由指数名称初步推断</t>
+清洗备注：策略大类由ESG/可持续标准化为ESG；标记为待校验；指数公司由指数名称初步推断
+Step7代表产品级别：补充观察代表；后续需看指数规则：可持续发展评分、样本空间、负面剔除机制</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -4569,15 +4667,20 @@
       <c r="Q59" s="2" t="n"/>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>体现港股通资产中的红利低波策略，适合作为跨境补充观察</t>
+        </is>
+      </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
           <t>待校验事项：属于港股通/跨境方向，暂不混入A股主线
 清洗备注：标记为待校验；指数公司由指数名称初步推断
-Step 6 分类修正备注：后续需要和mentor确认港股通产品是否纳入境内部分</t>
+Step 6 分类修正备注：后续需要和mentor确认港股通产品是否纳入境内部分
+Step7代表产品级别：跨境补充代表；后续需看指数规则：港股通样本空间、低波和红利筛选方式、汇率/市场差异</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">

--- a/02_outputs/excel/境内策略ETF产品梳理_初版.xlsx
+++ b/02_outputs/excel/境内策略ETF产品梳理_初版.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'产品总表'!$A$1:$U$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'策略分类表'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'指数规则表'!$A$1:$P$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'指数规则表'!$A$1:$P$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4774,25 +4774,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="52" customWidth="1" min="11" max="11"/>
+    <col width="51" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="14" max="14"/>
+    <col width="52" customWidth="1" min="15" max="15"/>
+    <col width="52" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -4877,8 +4877,2140 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>红利</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>上证红利指数</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>000015</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>上证/中证</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>上证180指数样本空间中满足市值、成交额、连续分红和股利支付率条件的沪市A股及红筹企业存托凭证</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>过去三年平均现金股息率、连续分红、股利支付率、规模、流动性</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>在样本空间内按过去三年平均现金股息率由高到低排名，选取前50只证券</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>股息率加权</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>每年12月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>单只样本权重不超过10%；总市值100亿元以下样本权重不超过1%</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>无明确行业上限</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>传统沪市红利策略，强调高股息、分红稳定和可投资性，是境内红利ETF最经典的指数之一</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/000015_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>红利</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>中证红利指数</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>000922</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>中证全指指数样本空间中满足市值、成交额、连续分红和股利支付率条件的A股及红筹企业存托凭证</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>过去三年平均现金股息率、连续分红、股利支付率、规模、流动性</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>在样本空间内按过去三年平均现金股息率由高到低排名，选取前100只上市公司证券</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>股息率加权</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>每年12月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>单只样本权重不超过10%；总市值100亿元以下样本权重不超过0.5%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>无明确行业上限</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>A股全市场红利代表指数，较上证红利覆盖范围更广，是中证体系红利策略的核心</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208175433-000922_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>红利</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>深证红利指数</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>399324</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>深证/国证</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>深市A股</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>累计分红金额、日均成交金额、ROE相关条件</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>国证官网公开页面显示：剔除预期净资产收益率处于后50%且净资产收益率变化率处于后20%的股票，选取累计分红金额和日均成交金额综合排名位于前40名的股票作为样本股</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>待二次核验；公开页面未完整展示权重细则</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>待二次核验</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>待二次核验</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>待二次核验</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>深市红利代表指数，与上证红利和中证红利形成市场板块对比</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/module/index-detail.html?act_menu=1&amp;indexCode=399324</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>红利低波</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>中证红利低波动指数</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>H30269</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>中证全指指数样本空间中满足连续分红、市值和成交额条件的上市公司证券</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>股息率、波动率、红利支付率、每股股息增长率</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>先剔除红利支付率过高或为负、每股股息增长率非正的证券；再按三年平均税后现金股息率选前75只；最后按过去一年波动率升序选前50只</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>股息率加权</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>每年12月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>单只样本权重不超过15%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>无明确行业上限</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>红利+低波复合策略，通过高股息和低波动筛选增强防御属性</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/H30269_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>红利低波</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>中证红利低波动100指数</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>930955</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>中证全指指数样本空间</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>股息率、过去一年波动率、连续分红、流动性</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>剔除过去一年日均成交金额排名后20%；选取过去三年连续现金分红且每年现金股息率大于0的证券；先按股息率选前300只，再按过去一年波动率升序选前100只</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>股息率/过去一年波动率加权</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>每季度调整；3月、6月、9月、12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>未给单只权重上限；明确中证二级行业权重不超过20%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>中证二级行业权重不超过20%</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>比中证红利低波动指数成分更多、更分散，使用股息率/波动率加权</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208180204-930955_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>红利低波</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>中证A500红利低波动指数</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>932422</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>中证A500指数样本</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>连续分红、股利支付率、ROE稳定性、股息率、波动率</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>在中证A500样本中选取过去三年连续现金分红、股利支付率合理、过去12个季度ROE标准差排名前80%的证券；按过去三年平均现金股息率选前50%作为待选样本；再按过去一年波动率升序选前50只</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>股息率加权</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>每半年调整；6月和12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>单只样本权重不超过10%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>单个一级行业权重不超过30%</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>A500样本空间上的红利低波策略，体现新宽基生态与红利低波因子的结合</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/932422_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>国证自由现金流指数</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>980092</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>国证</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>满足非ST、上市时间、无重大违规、经营正常、价格无异常波动等条件的A股和红筹企业存托凭证</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流率、ROE稳定性、经营现金流质量、流动性、行业剔除</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>剔除最近半年日均成交金额后20%、金融或房地产行业、近12季度ROE稳定性后10%；选取自由现金流、企业价值和近三年经营现金流为正且现金流质量较好的证券；按近一年自由现金流率选前100只</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>按样本公司自由现金流计算初始权重</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>每季度调整；3月、6月、9月、12月第二个星期五的下一个交易日实施</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>单只样本权重不超过10%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>剔除金融和房地产行业</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>强调企业真实现金创造能力和现金流稳定性，是自由现金流策略核心指数</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/docs/gz_980092.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>中证全指自由现金流指数</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>932365</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>中证全指指数样本空间</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流率、自由现金流、企业价值、连续经营现金流、盈利质量、流动性</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>过去一年日均成交金额排名位于前80%；剔除金融和地产；要求自由现金流和企业价值为正、连续5年经营现金流为正、盈利质量前80%；按自由现金流率选前100只</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流加权</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>每季度调整；3月、6月、9月、12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>单只样本权重不超过10%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>剔除金融和地产行业</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>中证体系自由现金流指数，便于和国证自由现金流进行规则差异对比</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/932365_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>红利质量</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>中证红利质量指数</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>931468</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>中证全指指数样本空间</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>连续分红、分红总额、再融资、股利支付率、盈利质量、毛利率、ROE均值-标准差、ROE变化</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>先做市值和成交额可投资性筛选；选取满足分红、再融资和股利支付率条件的证券；计算六个财务质量指标综合得分，选前50只</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>标准化后的综合得分加权</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>每半年调整；6月和12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>单只样本权重不超过10%；前五大样本权重合计不超过40%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>无明确行业上限</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>红利+质量复合策略，强调分红能力和盈利质量</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208180546-931468_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>红利质量</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>中证全指红利质量指数</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>932315</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>中证全指指数样本空间</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>连续分红、平均股利支付率、股息率、ROE稳定性、ROE、DROE、OPCFD、DP</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>先做市值和成交额筛选；选取过去三年连续分红且股利支付率合理证券；按股息率剔除后50%；按ROE标准差筛选；再按质量因子综合得分选前50只</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>综合得分倾斜加权</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>每半年调整；6月和12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>单只样本权重不超过10%；前五大样本权重合计不超过40%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>单个一级行业权重合计不超过30%</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>红利质量扩展指数，约束更强调分红稳定、质量和行业分散</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/932315_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>价值</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>中证国信价值指数</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>931052</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>中证全指指数样本空间中沪深市场证券</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>低估值、盈利能力、ESG风险、商誉、质押、流动性</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>先做流动性筛选；剔除大股东质押比例高、商誉占净资产比例高、ESG评级较低等证券；从具有长期价值增长潜力且估值较低证券中选取100只</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待进一步按编制方案完整核验；官方简介为价值策略样本</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>待进一步核验</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>待进一步核验</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>待进一步核验</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>富国中证价值ETF跟踪的核心价值因子指数，需重点核清完整权重细则</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208180210-931052_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>价值</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>国证价值100指数</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>980081</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>国证</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>满足非ST、上市时间条件的A股和红筹企业存托凭证</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>PE倒数、股息率、自由现金流率、ROE质量、自由现金流率、流动性、市值、盈利条件</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>剔除近半年成交金额后20%、近半年总市值后20%、净利润小于0证券；剔除ROE均值后20%、ROE波动率前20%、自由现金流率后50%；对市盈率倒数、股息率、自由现金流率标准化后计算价值得分，选前100只</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>以价值得分倾斜因子乘自由流通市值计算初始权重</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>每季度调整；3月、6月、9月、12月第二个星期五的下一个交易日实施</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>单只样本权重不超过8%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>单个国证二级行业权重不超过20%</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>国证价值指数体系代表，实际是价值+质量约束的复合价值策略</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/docs/gz_980081.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>成长</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>创业板动量成长指数</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>399296</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>国证/深证</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>深圳证券交易所创业板上市交易且满足非ST、上市时间、财务和价格正常条件的A股</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>成长因子、动量因子、自由流通市值</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>先按过去半年日均自由流通市值选前30%；计算成长和动量六个指标得分；根据因子得分和自由流通市值进行倾斜，选前50只</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>自由流通市值权重基础上的因子倾斜加权</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>每季度调整；3月、6月、9月、12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>单只股票权重上限不超过15%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>成长因子得分按行业归一化处理；无明确行业权重上限</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>成长+动量复合策略，适合观察成长因子与趋势动量结合</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/docs/gz_399296.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>成长</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>深证成长40指数</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>399326</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>国证/深证</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>深圳证券交易所上市交易且满足非ST、上市时间、财务和价格正常条件的A股</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>成长因子、动量因子、流动性、市值、扣非净利润</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>剔除最近半年日均成交金额或日均总市值后30%、扣非净利润TTM小于0股票；优先纳入成长因子排名靠前的上期样本；剩余股票中选成长因子排名靠前且行业内自由流通市值靠前、动量得分较高证券，共40只</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>派氏加权；具体权重调整因子见国证维护细则</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>每季度调整；3月、6月、9月、12月第二个星期五的下一个交易日实施</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>未在摘要中明确单只权重上限</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>通过国证三级行业内排名筛选控制行业代表性</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>深市成长风格代表指数，兼顾成长得分和行业内动量表现</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.cnindex.com.cn/docs/gz_399326.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>成长</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>上证科创板成长指数</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>000690</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>上证/中证</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>满足上市时间和非退市风险警示条件的科创板股票及红筹企业存托凭证</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>营收增长、扣非净利润增长、增长趋势、流动性</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>过去一年日均成交金额排名前90%；计算最新季度营收TTM环比增长率、扣非净利润TTM环比增长率、过去12季度相关增长率和增长趋势，综合得分选前50只</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>自由流通市值调整后的市值加权并设权重因子</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>每季度调整；3月、6月、9月、12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>单个样本权重不超过10%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>无明确行业上限</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>科创板内部成长风格代表，体现成长因子与科创板样本空间结合</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/000690_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>低波</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪深300行业中性低波动指数</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>930846</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>沪深300指数样本</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>过去一年日收益率波动率、行业中性</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>在沪深300一级行业内计算过去一年日收益率波动率并由低到高排名；按沪深300一级行业样本分布确定行业配额，选取低波证券并调整至100只</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>行业权重保持与沪深300一级行业权重相同；行业内按波动率倒数加权</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>每半年调整；6月和12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>未设普通单只权重上限；权重由行业权重和波动率倒数决定</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>保持沪深300一级行业中性</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>大盘低波策略，核心是降低波动同时减少行业偏离</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/527_930846_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>低波</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>中证500行业中性低波动指数</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>930782</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>中证500指数样本</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>过去一年日收益率波动率、行业中性</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>在中证500二级行业内计算过去一年日收益率波动率并排序；按中证500二级行业样本分布确定配额，选取低波证券并调整至150只</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>行业内按波动率倒数加权</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>每半年调整；6月和12月第二个星期五的下一交易日实施</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>未设普通单只权重上限；权重由行业权重和波动率倒数决定</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>保持中证500二级行业中性</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>中盘低波策略，与沪深300低波形成市值层面对比</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/480_930782_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>基本面策略</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>中证锐联基本面50指数</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>000925/399925</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>中证全指指数样本空间</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>营业收入、现金流、净资产、分红、流动性</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>剔除过去一年日均成交金额排名后20%；计算过去5年营业收入、现金流、净资产、分红四项基本面指标的相对占比，得到基本面价值，选基本面价值最大前50只</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>经自由流通比例调整后的基本面价值加权</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>每年6月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>未在摘要中明确单只权重上限</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>无明确行业上限</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>非市值加权代表策略，用基本面经济规模替代市值权重</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208175416-000925_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>基本面策略</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>深证基本面120指数</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>399702</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>深证/中证</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>满足上市时间和非ST条件的深市证券</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>营业收入、现金流、净资产、分红、流动性</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>剔除过去一年日均成交金额排名后20%；计算基本面价值，选取基本面价值排名前120名证券</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>经自由流通比例调整后的基本面价值加权</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>每年6月第二个星期五的下一交易日调整</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>未在摘要中明确单只权重上限</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>无明确行业上限</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>深市基本面加权策略代表，适合与基本面50对比样本空间和成分数量</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/289_399701_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>指数增强/多因子</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>中证800+指数增强</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锚定中证800宽基指数</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>多因子Alpha策略、跟踪误差约束、组合优化</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>该产品属于指数增强ETF，不是跟踪预先编制的Smart Beta策略指数；应查基金招募说明书中的增强策略和跟踪误差约束</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>指数增强ETF应单列观察，不与纯策略指数ETF混入同一规则表比较</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>待补充基金招募说明书URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>指数增强/多因子</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>中证A500+增强策略</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>锚定中证A500宽基指数</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>多因子增强、主动偏离约束、跟踪误差控制</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>该产品属于指数增强ETF，不是跟踪预先编制的Smart Beta策略指数；应查基金招募说明书中的增强策略和跟踪误差约束</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>不适用</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>A500生态下指数增强代表，需单独作为增强ETF观察样本</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>待补充基金招募说明书URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>央国企红利/股东回报</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>中证国新央企股东回报指数</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>932039</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>中证全指指数样本空间中国务院国资委央企名录或实际控制权/第一大股东归属于国务院国资委的上市公司证券</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>现金分红或回购总额占总市值比率、市值、成交额、央企属性</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>主要选取国务院国资委下属现金分红或回购总额占总市值比率较高的50只上市公司证券</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待进一步查完整加权规则；指数目标为股东回报主题</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>每年调整</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>待进一步核验</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>央企样本空间限定</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>中国特色股东回报策略，兼具央企主题和分红/回购回报属性</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208180042-932039_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>央国企红利/股东回报</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>中证中央企业红利指数</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>000825</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>中证全指指数样本空间中实际控制人为国务院国资委或财政部，且满足市值、成交额等条件的A股及红筹企业存托凭证</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>央企属性、现金股息率、分红稳定性、规模、流动性</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>从中央企业中选取现金股息率高、分红比较稳定且有一定规模及流动性的50只证券</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待进一步查完整加权规则；大概率为股息率相关加权，需二次核验</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待进一步核验</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>待进一步核验</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>央企样本空间限定</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>央企范围内的红利策略，是红利策略的中国特色延伸</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/20231208175355-000825_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>中证诚通央企ESG指数</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>央企上市公司证券</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>央企属性、中证ESG评价得分</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>公开新闻显示该指数依据中证ESG评价中环境、社会、公司治理评价得分，选取ESG综合得分最高的50只央企上市公司证券；完整编制方案需后续在中证官网二次核验</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待二次核验</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待二次核验</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>待二次核验</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>央企样本空间限定</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>央企主题和ESG评分结合，暂作为ESG补充观察</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.sse.com.cn/disclosure/fund/announcement/c/new/2024-12-10/560810_20241210_D138.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>中证可持续发展100指数</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>931268</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>中证</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>沪深300指数样本</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>可持续发展评分、ESG/可持续发展评估、负面剔除</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>先从产业政策、特殊行业、财务问题、负面事件、违法违规及特殊处理等方面剔除不符合资质证券，再基于可持续发展评估模型选取评分最高的100家上市公司证券</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待进一步核验完整权重细则</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待进一步核验</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>待进一步核验</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>以沪深300为样本空间，无明确行业上限</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>可持续发展/ESG策略补充样本，不作为今天A股因子主线</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>https://oss-ch.csindex.com.cn/static/html/csindex/public/uploads/indices/detail/files/zh_CN/1645_931268_Index_Methodology_cn.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>港股通红利/低波</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>标普港股通低波红利指数</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>标普道琼斯</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>标普港股通指数</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>股息收益率、波动率、港股通可投资性</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>标普官网说明该指数用于衡量标普港股通指数内50只波幅最小、收益率高的股票表现；完整规则见标普低波红利指数编制方法</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待进一步查标普方法论细则</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待进一步核验</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>待进一步核验</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>港股通样本空间限定</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/指数官网factsheet实时导出</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>港股通低波红利策略，属于跨境补充，不混入境内A股主线</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.spglobal.com/spdji/zh/indices/dividends-factors/sp-access-hong-kong-low-volatility-high-dividend-index/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P1"/>
+  <autoFilter ref="A1:P27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/02_outputs/excel/境内策略ETF产品梳理_初版.xlsx
+++ b/02_outputs/excel/境内策略ETF产品梳理_初版.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'产品总表'!$A$1:$U$59</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'策略分类表'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'策略分类表'!$A$1:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'指数规则表'!$A$1:$P$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4701,18 +4701,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -4762,8 +4762,713 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>红利</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>股息率、连续分红、股利支付率、流动性</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>通过高股息和稳定分红获取防御型收益，兼具低估值和现金回报属性</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>上证红利指数；中证红利指数；深证红利指数</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>510880 华泰柏瑞上证红利ETF；515080 招商中证红利ETF；159905 工银深证红利ETF</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>低利率、震荡市、弱市防御、长期现金流配置</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>红利陷阱、行业集中、周期行业占比高、分红持续性下降</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>成熟度高</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>当前境内策略 ETF 最成熟主线之一，产品数量、规模和投资者认知度较高</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>红利低波</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>股息率、低波动、连续分红、股利支付率</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>在红利策略基础上加入低波动筛选，追求股息收益和回撤控制</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>中证红利低波动指数；中证红利低波动100指数；中证A500红利低波动指数</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>512890 华泰柏瑞中证红利低波动ETF；515100 景顺长城中证红利低波动100ETF；563510 易方达中证A500红利低波动ETF</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>弱市、震荡市、低利率环境、防御型配置</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>牛市弹性不足、低波因子拥挤、行业集中或调样带来风格偏离</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>成熟度较高</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>红利策略的重要衍生方向，是“红利+”中最有规模基础的类别</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流率、自由现金流、经营现金流质量、ROE稳定性</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>关注企业真实现金创造能力，弱化会计利润噪音</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>国证自由现金流指数；中证全指自由现金流指数</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>159201 华夏国证自由现金流ETF；159222 易方达国证自由现金流ETF；159233 平安中证全指自由现金流ETF</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>重视盈利质量、现金回报和企业经营韧性的市场环境</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>策略认知仍在建立、行业剔除带来偏离、周期行业现金流波动</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>快速发展</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>近年增长较快，是红利之后较值得重点关注的新兴策略方向</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>红利质量</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>分红稳定性、股息率、ROE、盈利质量、毛利率、现金流质量</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>在红利基础上加入质量约束，试图规避单纯高股息带来的红利陷阱</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>中证红利质量指数；中证全指红利质量指数</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>159758 华夏中证红利质量ETF；159209 招商中证全指红利质量ETF</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>震荡市、红利行情升级、投资者希望兼顾分红和基本面质量时</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>因子叠加后逻辑复杂，可能牺牲部分股息率，规模和认知仍需培育</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>新兴复合策略</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>建议作为“红利+质量”单列，而不是简单放入纯质量类</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>质量</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ROE、ROA、盈利稳定性、低杠杆、现金流质量、毛利率</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>选择盈利能力强、财务稳健、经营质量较高的公司</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>沪深300质量指数；中证质量指数等</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>当前产品池未系统纳入纯质量ETF，后续需补充</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>长期配置、盈利分化、好公司占优阶段</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>估值偏高、成长风格回撤、质量因子阶段性失效</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>已有布局但当前表需补充</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>当前产品池主要覆盖“红利质量”，纯质量 ETF 后续应通过 Wind / Choice 补齐</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>价值</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>低估值、PE、PB、股息率、自由现金流率、盈利约束</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>买入低估值且具备一定盈利质量的公司，等待估值修复</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>中证国信价值指数；国证价值100指数</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>512040 富国中证价值ETF；159263 易方达国证价值100ETF</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>经济修复、低估值风格占优、风险偏好修复阶段</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>价值陷阱、长期低估、周期行业拖累</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>价值类已有产品布局，但规模和市场认知通常弱于红利类</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>成长</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>营收增长、净利润增长、成长因子、动量因子</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>选择收入和利润增长较快、景气度较高的公司</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>创业板动量成长指数；深证成长40指数；上证科创板成长指数</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>159967 华夏创业板动量成长ETF；159906 大成深证成长40ETF；588020 易方达上证科创板成长ETF</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>景气上行、风险偏好提升、科技成长行情</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>高估值、高波动、回撤较大、主题属性与策略属性容易混淆</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>中等</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>成长策略常和创业板、科创板等板块结合，需要区分“策略因子”和“主题暴露”</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>低波</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>历史波动率、波动率倒数、行业中性约束</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>降低组合波动和回撤，同时通过行业中性减少行业偏离</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>沪深300行业中性低波动指数；中证500行业中性低波动指数</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>512270 华安沪深300行业中性低波ETF；512260 华安中证500行业中性低波ETF</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>弱市、震荡市、机构稳健配置需求</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>牛市跑输、低波拥挤、行业约束导致收益弹性不足</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>小众但规则清晰</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>低波策略逻辑清楚，但境内产品规模和热度相对有限</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>基本面策略</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>营业收入、现金流、净资产、分红、基本面价值</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>用企业基本面经济规模替代市值作为权重依据，弱化价格波动影响</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>中证锐联基本面50指数；深证基本面120指数</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>512750 嘉实基本面50ETF；159910 嘉实深证基本面120ETF</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>市值加权失真、价值风格占优、投资者关注企业基本面权重时</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>偏传统行业，策略认知度有限，可能长期跑输成长风格</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>经典但热度一般</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>属于另类加权 / 基本面加权方向，适合和海外 Fundamental ETF 对比</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>指数增强/多因子</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>多因子Alpha、量化选股、组合优化、跟踪误差控制</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锚定宽基指数，在控制跟踪误差下追求超额收益</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>中证800增强；中证A500增强策略</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>159517 银华中证800增强ETF；512370 华夏中证A500增强策略ETF</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>宽基配置基础上希望获取一定超额收益时</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>模型失效、跟踪误差、主动管理边界不清</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>单列观察</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>指数增强 ETF 不等同于纯 Smart Beta ETF，建议单列，不混入主线</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>央国企红利/股东回报</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>央企/国企属性、分红、回购、股息率、股东回报</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>结合央国企主题和红利/股东回报策略，体现中国特色估值重估逻辑</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>中证国新央企股东回报指数；中证中央企业红利指数</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>561960 招商中证国新央企股东回报ETF；561580 华泰柏瑞中证中央企业红利ETF</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>国企改革、中特估、红利行情、政策支持阶段</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>主题属性较强、行业集中、政策预期波动</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>补充观察</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>可作为红利策略的中国特色延伸，是否纳入主线需和 mentor 确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>ESG评分、可持续发展评分、负面剔除、治理质量</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>通过环境、社会、治理或可持续发展评价筛选公司</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>中证诚通央企ESG指数；中证可持续发展100指数</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>560810 融通中证诚通央企ESGETF；515090 博时中证可持续发展100ETF</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>长期资金、机构配置、ESG主题需求提升阶段</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>国内投资者认知有限，评分体系差异，策略收益解释难度较高</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>补充观察</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>ESG 可作为扩展方向，暂不作为今天主线</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>港股通红利/低波</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>港股通范围、高股息、低波动、央企红利</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>在港股通资产中寻找高股息和低波动机会</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>标普港股通低波红利指数；港股通央企红利相关指数</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>159118 华夏标普港股通低波红利ETF</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>港股低估值、高股息、南向资金配置阶段</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>港股市场波动、汇率影响、流动性和行业集中</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>跨境补充</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>在境内上市但底层为港股通资产，不建议混入 A 股主线</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>等权/另类加权</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>等权、风险权重、基本面权重、非市值加权</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>通过改变传统市值加权方式，减少大市值股票权重过高的问题</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>沪深300等权；中证500等权等</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>当前产品池未系统纳入，后续需补充</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>市值权重失衡、风格轮动、小盘或均衡配置占优时</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>换手较高、流动性压力、可能偏离主流宽基表现</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>研报 117 只口径通常会纳入等权和另类加权，后续应通过 Wind / Choice 补齐</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>动量</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>价格动量、趋势延续、相对强弱</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>捕捉强势股票的趋势延续效应</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>沪深300动量；中证500动量等</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>当前产品池未系统纳入纯动量ETF，159967 含成长+动量属性</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>趋势行情、风险偏好提升、强者恒强阶段</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>反转行情回撤大、换手较高、因子拥挤</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待补充</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>当前成长类中已有动量成长产品，但纯动量 ETF 后续仍需补充</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/02_outputs/excel/境内策略ETF产品梳理_初版.xlsx
+++ b/02_outputs/excel/境内策略ETF产品梳理_初版.xlsx
@@ -10,11 +10,15 @@
     <sheet name="产品总表" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="策略分类表" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="指数规则表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="统计分析" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="初步发现" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'产品总表'!$A$1:$U$59</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'策略分类表'!$A$1:$I$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'指数规则表'!$A$1:$P$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'统计分析'!$A$1:$E$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'初步发现'!$A$1:$B$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,6 +43,11 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -72,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -81,6 +90,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7718,4 +7736,1010 @@
   <autoFilter ref="A1:P27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>统计模块</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>统计项目</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>产品总览</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>当前产品池产品总数</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>当前核心产品池</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品总览</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>主线产品数量</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>建议纳入级别=主线</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>产品总览</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>补充观察产品数量</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>0.1724137931034483</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>建议纳入级别=补充观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>产品总览</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>单列观察产品数量</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>建议纳入级别=单列观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>产品总览</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>跨境补充产品数量</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>0.05172413793103448</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>建议纳入级别=跨境补充</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>产品总览</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>仅作线索产品数量</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.05172413793103448</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>建议纳入级别=仅作线索</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>产品总览</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>待校验产品数量</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>0.7241379310344828</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>是否待校验=是</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>产品总览</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Step7代表产品数量</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.4655172413793103</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>是否Step7代表产品=是</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>产品总览</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>非代表产品数量</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>0.5344827586206896</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>未入选Step7代表产品</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>策略大类</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>红利</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.1724137931034483</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>主线10；待校验6；代表产品3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>策略大类</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>自由现金流</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>0.1724137931034483</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>主线7；待校验10；代表产品3</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>策略大类</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>红利低波</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.1379310344827586</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>主线8；待校验5；代表产品3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>策略大类</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>央国企红利/股东回报</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>主线0；待校验7；代表产品2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>策略大类</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>成长</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.103448275862069</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>主线6；待校验2；代表产品3</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>策略大类</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>ESG</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.05172413793103448</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>主线0；待校验3；代表产品2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>策略大类</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>港股通红利/低波</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0.05172413793103448</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>主线0；待校验3；代表产品1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>策略大类</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>红利质量</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0.05172413793103448</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>主线3；待校验2；代表产品2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>策略大类</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>价值</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>主线2；待校验2；代表产品2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>策略大类</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>低波</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>主线2；待校验0；代表产品2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>策略大类</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>基本面策略</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>主线2；待校验0；代表产品2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>策略大类</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>指数增强/多因子</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>主线0；待校验2；代表产品2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>主线</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0.6896551724137931</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>补充观察</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0.1724137931034483</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>单列观察</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.03448275862068965</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>跨境补充</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>0.05172413793103448</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>仅作线索</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.05172413793103448</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>纳入级别</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>其他或待判断</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>代表产品</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Step7代表产品总数</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>代表产品</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>主线</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>按建议纳入级别</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>代表产品</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>补充观察</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>按建议纳入级别</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>代表产品</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>单列观察</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.07407407407407407</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>按建议纳入级别</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>代表产品</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>跨境补充</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.03703703703703703</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>按建议纳入级别</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>代表产品</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>仅作线索</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>按建议纳入级别</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>指数规则</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>指数规则总数</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr"/>
+      <c r="E35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>指数规则</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>已核验数量</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>指数规则</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>部分核验数量</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr"/>
+      <c r="E37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>指数规则</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>待二次核验数量</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>指数规则</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>指数增强单列观察数量</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>指数规则</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>前十大成分股待补充数量</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>指数规则</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>行业分布待补充数量</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr"/>
+      <c r="E41" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E41"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="68" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>标题</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>1. 当前产品池覆盖情况</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>当前产品池共58只，其中主线40只、补充观察10只、单列观察2只、跨境补充3只。当前不是全量117只数据库，而是核心产品池初版。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2. 策略类型分布</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>当前产品数量较多的策略为红利（10只）、自由现金流（10只）、红利低波（8只）、央国企红利/股东回报（7只）、成长（6只）。红利、红利低波和自由现金流构成优先研究主线；当前样本较少的类别包括ESG（3只）、港股通红利/低波（3只）、红利质量（3只）、价值（2只）、低波（2只）、基本面策略（2只）、指数增强/多因子（2只）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>3. 代表产品情况</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Step7共筛选27只代表产品，其中主线代表产品20只，覆盖红利、红利低波、自由现金流、红利质量、价值、成长、低波和基本面策略等方向，后续用于指数规则拆解。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>4. 指数规则整理情况</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>已整理26条代表指数规则，其中已核验17条、部分核验7条、待二次核验2条。前十大成分股和行业分布需后续通过Wind、Choice或指数官网factsheet补齐。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>5. 初步判断</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>境内策略ETF已由单一红利扩展至红利低波、自由现金流、红利质量、价值、成长、低波和基本面策略。当前核心产品池中，红利、红利低波、自由现金流最值得优先展开；红利质量可作为红利策略升级方向。价值、成长、低波和基本面策略已有布局，但仍需结合规模和流动性判断成熟度。指数增强/多因子、央国企红利/股东回报、ESG、港股通红利/低波暂作为补充观察；纯质量、等权/另类加权和动量仍需补充。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>6. 后续待补充事项</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>待Wind/Choice到位后补充规模、成交额、费率、成立日期和上市日期；补齐全量117只策略ETF；补充纯质量、等权和动量等缺口；校验所有待校验产品；导出前十大成分股和行业分布。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B7"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>